--- a/www/flightdata/xlsx/eoss-357.xlsx
+++ b/www/flightdata/xlsx/eoss-357.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="516">
   <si>
     <t>flight</t>
   </si>
@@ -36,6 +36,18 @@
     <t>h2fill</t>
   </si>
   <si>
+    <t>maxaltitude</t>
+  </si>
+  <si>
+    <t>numpoints</t>
+  </si>
+  <si>
+    <t>flighttime</t>
+  </si>
+  <si>
+    <t>flighttime_secs</t>
+  </si>
+  <si>
     <t>weights.client</t>
   </si>
   <si>
@@ -73,6 +85,9 @@
   </si>
   <si>
     <t>301</t>
+  </si>
+  <si>
+    <t>1hrs 51mins 47secs</t>
   </si>
   <si>
     <t>6.21</t>
@@ -1910,10 +1925,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1953,46 +1968,70 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>89552</v>
+      </c>
+      <c r="H2">
+        <v>224</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>6707</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2007,102 +2046,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>45403.3397934838</v>
@@ -2120,13 +2159,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K2">
         <v>23</v>
@@ -2162,7 +2201,7 @@
         <v>6.6</v>
       </c>
       <c r="V2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="X2">
         <v>6.6</v>
@@ -2173,10 +2212,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>45403.33991818287</v>
@@ -2194,13 +2233,13 @@
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K3">
         <v>300</v>
@@ -2224,7 +2263,7 @@
         <v>17.7</v>
       </c>
       <c r="V3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W3">
         <v>0.37</v>
@@ -2247,10 +2286,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>45403.34010142361</v>
@@ -2268,13 +2307,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K4">
         <v>29</v>
@@ -2310,7 +2349,7 @@
         <v>22.56666667</v>
       </c>
       <c r="V4" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W4">
         <v>0.162222</v>
@@ -2339,10 +2378,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>45403.34025924769</v>
@@ -2360,13 +2399,13 @@
         <v>47</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J5" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K5">
         <v>337</v>
@@ -2390,7 +2429,7 @@
         <v>19.26666667</v>
       </c>
       <c r="V5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W5">
         <v>-0.11</v>
@@ -2419,10 +2458,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>45403.34048710648</v>
@@ -2440,13 +2479,13 @@
         <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K6">
         <v>354</v>
@@ -2482,7 +2521,7 @@
         <v>19.86666667</v>
       </c>
       <c r="V6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W6">
         <v>0.02</v>
@@ -2511,10 +2550,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>45403.34060564815</v>
@@ -2532,13 +2571,13 @@
         <v>77</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="K7">
         <v>55</v>
@@ -2562,7 +2601,7 @@
         <v>21.86666667</v>
       </c>
       <c r="V7" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W7">
         <v>0.066667</v>
@@ -2591,10 +2630,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>45403.3408002662</v>
@@ -2612,13 +2651,13 @@
         <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K8">
         <v>124</v>
@@ -2654,7 +2693,7 @@
         <v>22</v>
       </c>
       <c r="V8" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W8">
         <v>0.004444</v>
@@ -2683,10 +2722,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2">
         <v>45403.34095277778</v>
@@ -2704,13 +2743,13 @@
         <v>107</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K9">
         <v>12</v>
@@ -2734,7 +2773,7 @@
         <v>19.7</v>
       </c>
       <c r="V9" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W9">
         <v>-0.076667</v>
@@ -2763,10 +2802,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v>45403.34118518519</v>
@@ -2784,13 +2823,13 @@
         <v>120</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K10">
         <v>193</v>
@@ -2826,7 +2865,7 @@
         <v>20.03333333</v>
       </c>
       <c r="V10" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W10">
         <v>0.011111</v>
@@ -2855,10 +2894,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2">
         <v>45403.34130043982</v>
@@ -2876,13 +2915,13 @@
         <v>137</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K11">
         <v>37</v>
@@ -2906,7 +2945,7 @@
         <v>21.2</v>
       </c>
       <c r="V11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W11">
         <v>0.038889</v>
@@ -2935,10 +2974,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2">
         <v>45403.34148907408</v>
@@ -2956,13 +2995,13 @@
         <v>150</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="K12">
         <v>110</v>
@@ -2998,7 +3037,7 @@
         <v>21.26666667</v>
       </c>
       <c r="V12" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W12">
         <v>0.002222</v>
@@ -3027,10 +3066,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2">
         <v>45403.34164728009</v>
@@ -3048,13 +3087,13 @@
         <v>167</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K13">
         <v>163</v>
@@ -3078,7 +3117,7 @@
         <v>22.43333333</v>
       </c>
       <c r="V13" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W13">
         <v>0.038889</v>
@@ -3107,10 +3146,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
         <v>45403.34186986111</v>
@@ -3128,13 +3167,13 @@
         <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J14" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K14">
         <v>164</v>
@@ -3170,7 +3209,7 @@
         <v>23.06666667</v>
       </c>
       <c r="V14" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W14">
         <v>0.021111</v>
@@ -3199,10 +3238,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>45403.34199619213</v>
@@ -3220,13 +3259,13 @@
         <v>197</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="K15">
         <v>177</v>
@@ -3250,7 +3289,7 @@
         <v>21.96666667</v>
       </c>
       <c r="V15" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W15">
         <v>-0.036667</v>
@@ -3279,10 +3318,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2">
         <v>45403.34218773148</v>
@@ -3300,13 +3339,13 @@
         <v>210</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J16" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K16">
         <v>172</v>
@@ -3342,7 +3381,7 @@
         <v>21.93333333</v>
       </c>
       <c r="V16" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W16">
         <v>-0.001111</v>
@@ -3371,10 +3410,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2">
         <v>45403.34234268519</v>
@@ -3392,13 +3431,13 @@
         <v>227</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K17">
         <v>197</v>
@@ -3422,7 +3461,7 @@
         <v>22.86666667</v>
       </c>
       <c r="V17" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W17">
         <v>0.031111</v>
@@ -3451,10 +3490,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2">
         <v>45403.34257021991</v>
@@ -3472,13 +3511,13 @@
         <v>240</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K18">
         <v>147</v>
@@ -3514,7 +3553,7 @@
         <v>22.1</v>
       </c>
       <c r="V18" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W18">
         <v>-0.025556</v>
@@ -3543,10 +3582,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2">
         <v>45403.34268951389</v>
@@ -3564,13 +3603,13 @@
         <v>257</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K19">
         <v>136</v>
@@ -3594,7 +3633,7 @@
         <v>22</v>
       </c>
       <c r="V19" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W19">
         <v>-0.003333</v>
@@ -3623,10 +3662,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2">
         <v>45403.34288285879</v>
@@ -3644,13 +3683,13 @@
         <v>270</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K20">
         <v>149</v>
@@ -3686,7 +3725,7 @@
         <v>21.93333333</v>
       </c>
       <c r="V20" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W20">
         <v>-0.002222</v>
@@ -3715,10 +3754,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2">
         <v>45403.34303712963</v>
@@ -3736,13 +3775,13 @@
         <v>287</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K21">
         <v>110</v>
@@ -3766,7 +3805,7 @@
         <v>21.2</v>
       </c>
       <c r="V21" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W21">
         <v>-0.024444</v>
@@ -3795,10 +3834,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2">
         <v>45403.34326444445</v>
@@ -3816,13 +3855,13 @@
         <v>300</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K22">
         <v>157</v>
@@ -3858,7 +3897,7 @@
         <v>21.63333333</v>
       </c>
       <c r="V22" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W22">
         <v>0.014444</v>
@@ -3887,10 +3926,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>45403.34338399306</v>
@@ -3908,13 +3947,13 @@
         <v>317</v>
       </c>
       <c r="H23" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K23">
         <v>161</v>
@@ -3938,7 +3977,7 @@
         <v>20.8</v>
       </c>
       <c r="V23" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W23">
         <v>-0.027778</v>
@@ -3967,10 +4006,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2">
         <v>45403.34357177083</v>
@@ -3988,13 +4027,13 @@
         <v>330</v>
       </c>
       <c r="H24" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K24">
         <v>156</v>
@@ -4030,7 +4069,7 @@
         <v>21.56666667</v>
       </c>
       <c r="V24" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W24">
         <v>0.025556</v>
@@ -4059,10 +4098,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2">
         <v>45403.34395445602</v>
@@ -4080,13 +4119,13 @@
         <v>360</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K25">
         <v>125</v>
@@ -4122,7 +4161,7 @@
         <v>22.76666667</v>
       </c>
       <c r="V25" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W25">
         <v>0.04</v>
@@ -4151,10 +4190,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2">
         <v>45403.34427366898</v>
@@ -4172,13 +4211,13 @@
         <v>390</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K26">
         <v>143</v>
@@ -4214,7 +4253,7 @@
         <v>21.36666667</v>
       </c>
       <c r="V26" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W26">
         <v>-0.046667</v>
@@ -4243,10 +4282,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
         <v>45403.34442540509</v>
@@ -4264,13 +4303,13 @@
         <v>407</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K27">
         <v>153</v>
@@ -4294,7 +4333,7 @@
         <v>22.42222222</v>
       </c>
       <c r="V27" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W27">
         <v>0.011728</v>
@@ -4323,10 +4362,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2">
         <v>45403.34464880787</v>
@@ -4344,13 +4383,13 @@
         <v>420</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K28">
         <v>145</v>
@@ -4386,7 +4425,7 @@
         <v>22.36666667</v>
       </c>
       <c r="V28" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W28">
         <v>-0.001852</v>
@@ -4415,10 +4454,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2">
         <v>45403.34477232639</v>
@@ -4436,13 +4475,13 @@
         <v>437</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K29">
         <v>150</v>
@@ -4466,7 +4505,7 @@
         <v>21.76666667</v>
       </c>
       <c r="V29" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W29">
         <v>-0.02</v>
@@ -4495,10 +4534,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2">
         <v>45403.34511964121</v>
@@ -4516,13 +4555,13 @@
         <v>467</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K30">
         <v>163</v>
@@ -4546,7 +4585,7 @@
         <v>21.43333333</v>
       </c>
       <c r="V30" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W30">
         <v>-0.011111</v>
@@ -4575,10 +4614,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2">
         <v>45403.34534288194</v>
@@ -4596,13 +4635,13 @@
         <v>480</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J31" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K31">
         <v>158</v>
@@ -4638,7 +4677,7 @@
         <v>21.58333333</v>
       </c>
       <c r="V31" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W31">
         <v>0.0025</v>
@@ -4667,10 +4706,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2">
         <v>45403.34546665509</v>
@@ -4688,13 +4727,13 @@
         <v>497</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K32">
         <v>172</v>
@@ -4718,7 +4757,7 @@
         <v>21.96666667</v>
       </c>
       <c r="V32" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W32">
         <v>0.012778</v>
@@ -4747,10 +4786,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2">
         <v>45403.34581424769</v>
@@ -4768,13 +4807,13 @@
         <v>527</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="K33">
         <v>157</v>
@@ -4798,7 +4837,7 @@
         <v>24.16666667</v>
       </c>
       <c r="V33" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W33">
         <v>0.073333</v>
@@ -4827,10 +4866,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2">
         <v>45403.3460388426</v>
@@ -4848,13 +4887,13 @@
         <v>540</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J34" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K34">
         <v>157</v>
@@ -4890,7 +4929,7 @@
         <v>23.33333333</v>
       </c>
       <c r="V34" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W34">
         <v>-0.013889</v>
@@ -4919,10 +4958,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2">
         <v>45403.34616277778</v>
@@ -4940,13 +4979,13 @@
         <v>557</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J35" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K35">
         <v>129</v>
@@ -4970,7 +5009,7 @@
         <v>22.76666667</v>
       </c>
       <c r="V35" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W35">
         <v>-0.018889</v>
@@ -4999,10 +5038,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2">
         <v>45403.34635535879</v>
@@ -5020,13 +5059,13 @@
         <v>570</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K36">
         <v>145</v>
@@ -5062,7 +5101,7 @@
         <v>22.53333333</v>
       </c>
       <c r="V36" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W36">
         <v>-0.007778</v>
@@ -5091,10 +5130,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2">
         <v>45403.34651185185</v>
@@ -5112,13 +5151,13 @@
         <v>587</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J37" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K37">
         <v>163</v>
@@ -5142,7 +5181,7 @@
         <v>22.73333333</v>
       </c>
       <c r="V37" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W37">
         <v>0.006667</v>
@@ -5171,10 +5210,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2">
         <v>45403.34685717593</v>
@@ -5192,13 +5231,13 @@
         <v>617</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I38" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J38" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K38">
         <v>152</v>
@@ -5222,7 +5261,7 @@
         <v>24.06666667</v>
       </c>
       <c r="V38" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W38">
         <v>0.044444</v>
@@ -5251,10 +5290,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>45403.34720423611</v>
@@ -5272,13 +5311,13 @@
         <v>647</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I39" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K39">
         <v>152</v>
@@ -5302,7 +5341,7 @@
         <v>22.53333333</v>
       </c>
       <c r="V39" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W39">
         <v>-0.051111</v>
@@ -5331,10 +5370,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2">
         <v>45403.34755070602</v>
@@ -5352,13 +5391,13 @@
         <v>677</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J40" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K40">
         <v>137</v>
@@ -5382,7 +5421,7 @@
         <v>22.96666667</v>
       </c>
       <c r="V40" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W40">
         <v>0.014444</v>
@@ -5411,10 +5450,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C41" s="2">
         <v>45403.34789796297</v>
@@ -5432,13 +5471,13 @@
         <v>707</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J41" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K41">
         <v>157</v>
@@ -5462,7 +5501,7 @@
         <v>23.2</v>
       </c>
       <c r="V41" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W41">
         <v>0.007778</v>
@@ -5491,10 +5530,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2">
         <v>45403.34824575231</v>
@@ -5512,13 +5551,13 @@
         <v>737</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J42" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K42">
         <v>139</v>
@@ -5542,7 +5581,7 @@
         <v>23.4</v>
       </c>
       <c r="V42" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W42">
         <v>0.006667</v>
@@ -5571,10 +5610,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>45403.34843268518</v>
@@ -5592,13 +5631,13 @@
         <v>750</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I43" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J43" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K43">
         <v>150</v>
@@ -5634,7 +5673,7 @@
         <v>23.06666667</v>
       </c>
       <c r="V43" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W43">
         <v>-0.001852</v>
@@ -5663,10 +5702,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C44" s="2">
         <v>45403.34859243056</v>
@@ -5684,13 +5723,13 @@
         <v>767</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I44" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J44" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K44">
         <v>136</v>
@@ -5714,7 +5753,7 @@
         <v>22.76666667</v>
       </c>
       <c r="V44" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W44">
         <v>-0.01</v>
@@ -5743,10 +5782,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C45" s="2">
         <v>45403.34893930556</v>
@@ -5764,13 +5803,13 @@
         <v>797</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I45" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J45" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K45">
         <v>140</v>
@@ -5794,7 +5833,7 @@
         <v>24.26666667</v>
       </c>
       <c r="V45" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W45">
         <v>0.05</v>
@@ -5823,10 +5862,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C46" s="2">
         <v>45403.34929054398</v>
@@ -5844,13 +5883,13 @@
         <v>827</v>
       </c>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I46" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J46" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K46">
         <v>147</v>
@@ -5874,7 +5913,7 @@
         <v>24.83333333</v>
       </c>
       <c r="V46" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W46">
         <v>0.018889</v>
@@ -5903,10 +5942,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C47" s="2">
         <v>45403.3495095949</v>
@@ -5924,13 +5963,13 @@
         <v>840</v>
       </c>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I47" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J47" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K47">
         <v>150</v>
@@ -5966,7 +6005,7 @@
         <v>24.01111111</v>
       </c>
       <c r="V47" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W47">
         <v>-0.009136</v>
@@ -5995,10 +6034,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C48" s="2">
         <v>45403.34963349537</v>
@@ -6016,13 +6055,13 @@
         <v>857</v>
       </c>
       <c r="H48" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J48" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K48">
         <v>136</v>
@@ -6046,7 +6085,7 @@
         <v>22.1</v>
       </c>
       <c r="V48" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W48">
         <v>-0.063704</v>
@@ -6075,10 +6114,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C49" s="2">
         <v>45403.3499822338</v>
@@ -6096,13 +6135,13 @@
         <v>887</v>
       </c>
       <c r="H49" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I49" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J49" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K49">
         <v>145</v>
@@ -6126,7 +6165,7 @@
         <v>23.6</v>
       </c>
       <c r="V49" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W49">
         <v>0.05</v>
@@ -6155,10 +6194,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2">
         <v>45403.35020350695</v>
@@ -6176,13 +6215,13 @@
         <v>900</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J50" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K50">
         <v>138</v>
@@ -6218,7 +6257,7 @@
         <v>22.55</v>
       </c>
       <c r="V50" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W50">
         <v>-0.0175</v>
@@ -6247,10 +6286,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C51" s="2">
         <v>45403.35032831018</v>
@@ -6268,13 +6307,13 @@
         <v>917</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J51" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K51">
         <v>130</v>
@@ -6298,7 +6337,7 @@
         <v>21.76666667</v>
       </c>
       <c r="V51" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W51">
         <v>-0.026111</v>
@@ -6327,10 +6366,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>45403.3505168287</v>
@@ -6348,13 +6387,13 @@
         <v>930</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J52" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K52">
         <v>149</v>
@@ -6390,7 +6429,7 @@
         <v>22.16666667</v>
       </c>
       <c r="V52" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W52">
         <v>0.013333</v>
@@ -6419,10 +6458,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2">
         <v>45403.35067704861</v>
@@ -6440,13 +6479,13 @@
         <v>947</v>
       </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J53" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K53">
         <v>153</v>
@@ -6470,7 +6509,7 @@
         <v>21.43333333</v>
       </c>
       <c r="V53" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W53">
         <v>-0.024444</v>
@@ -6499,10 +6538,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>45403.35089872685</v>
@@ -6520,13 +6559,13 @@
         <v>960</v>
       </c>
       <c r="H54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J54" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K54">
         <v>141</v>
@@ -6562,7 +6601,7 @@
         <v>20.83333333</v>
       </c>
       <c r="V54" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W54">
         <v>-0.02</v>
@@ -6591,10 +6630,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C55" s="2">
         <v>45403.35102598379</v>
@@ -6612,13 +6651,13 @@
         <v>977</v>
       </c>
       <c r="H55" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I55" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J55" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K55">
         <v>131</v>
@@ -6642,7 +6681,7 @@
         <v>20.9</v>
       </c>
       <c r="V55" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W55">
         <v>0.002222</v>
@@ -6671,10 +6710,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C56" s="2">
         <v>45403.351369375</v>
@@ -6692,13 +6731,13 @@
         <v>1007</v>
       </c>
       <c r="H56" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I56" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J56" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K56">
         <v>130</v>
@@ -6722,7 +6761,7 @@
         <v>24.73333333</v>
       </c>
       <c r="V56" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W56">
         <v>0.127778</v>
@@ -6751,10 +6790,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C57" s="2">
         <v>45403.35159295139</v>
@@ -6772,13 +6811,13 @@
         <v>1020</v>
       </c>
       <c r="H57" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I57" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J57" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K57">
         <v>146</v>
@@ -6814,7 +6853,7 @@
         <v>23.51666667</v>
       </c>
       <c r="V57" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W57">
         <v>-0.020278</v>
@@ -6843,10 +6882,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C58" s="2">
         <v>45403.35172105324</v>
@@ -6864,13 +6903,13 @@
         <v>1037</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J58" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K58">
         <v>148</v>
@@ -6894,7 +6933,7 @@
         <v>22.86666667</v>
       </c>
       <c r="V58" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W58">
         <v>-0.021667</v>
@@ -6923,10 +6962,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2">
         <v>45403.35206660879</v>
@@ -6944,13 +6983,13 @@
         <v>1067</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I59" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J59" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K59">
         <v>129</v>
@@ -6974,7 +7013,7 @@
         <v>22.73333333</v>
       </c>
       <c r="V59" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W59">
         <v>-0.004444</v>
@@ -7003,10 +7042,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C60" s="2">
         <v>45403.35228770833</v>
@@ -7024,13 +7063,13 @@
         <v>1080</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J60" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K60">
         <v>129</v>
@@ -7066,7 +7105,7 @@
         <v>23.1</v>
       </c>
       <c r="V60" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W60">
         <v>0.006111</v>
@@ -7095,10 +7134,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C61" s="2">
         <v>45403.35241101852</v>
@@ -7116,13 +7155,13 @@
         <v>1097</v>
       </c>
       <c r="H61" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J61" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K61">
         <v>125</v>
@@ -7146,7 +7185,7 @@
         <v>24.16666667</v>
       </c>
       <c r="V61" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W61">
         <v>0.035556</v>
@@ -7175,10 +7214,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C62" s="2">
         <v>45403.35275898148</v>
@@ -7196,13 +7235,13 @@
         <v>1127</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I62" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J62" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K62">
         <v>132</v>
@@ -7226,7 +7265,7 @@
         <v>23.53333333</v>
       </c>
       <c r="V62" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W62">
         <v>-0.021111</v>
@@ -7255,10 +7294,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2">
         <v>45403.35298197917</v>
@@ -7276,13 +7315,13 @@
         <v>1140</v>
       </c>
       <c r="H63" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J63" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K63">
         <v>138</v>
@@ -7318,7 +7357,7 @@
         <v>23.7</v>
       </c>
       <c r="V63" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W63">
         <v>0.002778</v>
@@ -7347,10 +7386,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C64" s="2">
         <v>45403.353105625</v>
@@ -7368,13 +7407,13 @@
         <v>1157</v>
       </c>
       <c r="H64" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I64" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J64" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K64">
         <v>126</v>
@@ -7398,7 +7437,7 @@
         <v>25.56666667</v>
       </c>
       <c r="V64" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W64">
         <v>0.062222</v>
@@ -7427,10 +7466,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C65" s="2">
         <v>45403.35329466435</v>
@@ -7448,13 +7487,13 @@
         <v>1170</v>
       </c>
       <c r="H65" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I65" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J65" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K65">
         <v>135</v>
@@ -7490,7 +7529,7 @@
         <v>25.96666667</v>
       </c>
       <c r="V65" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W65">
         <v>0.013333</v>
@@ -7519,10 +7558,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C66" s="2">
         <v>45403.35345396991</v>
@@ -7540,13 +7579,13 @@
         <v>1187</v>
       </c>
       <c r="H66" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I66" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J66" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K66">
         <v>131</v>
@@ -7570,7 +7609,7 @@
         <v>25.26666667</v>
       </c>
       <c r="V66" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W66">
         <v>-0.023333</v>
@@ -7599,10 +7638,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C67" s="2">
         <v>45403.35367688657</v>
@@ -7620,13 +7659,13 @@
         <v>1200</v>
       </c>
       <c r="H67" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I67" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J67" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K67">
         <v>131</v>
@@ -7662,7 +7701,7 @@
         <v>25.56666667</v>
       </c>
       <c r="V67" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W67">
         <v>0.01</v>
@@ -7691,10 +7730,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C68" s="2">
         <v>45403.35380072916</v>
@@ -7712,13 +7751,13 @@
         <v>1217</v>
       </c>
       <c r="H68" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I68" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J68" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K68">
         <v>133</v>
@@ -7742,7 +7781,7 @@
         <v>25.83333333</v>
       </c>
       <c r="V68" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W68">
         <v>0.008888999999999999</v>
@@ -7771,10 +7810,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C69" s="2">
         <v>45403.35414768518</v>
@@ -7792,13 +7831,13 @@
         <v>1247</v>
       </c>
       <c r="H69" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I69" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J69" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K69">
         <v>144</v>
@@ -7822,7 +7861,7 @@
         <v>27.13333333</v>
       </c>
       <c r="V69" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W69">
         <v>0.043333</v>
@@ -7851,10 +7890,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C70" s="2">
         <v>45403.35437109954</v>
@@ -7872,13 +7911,13 @@
         <v>1260</v>
       </c>
       <c r="H70" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I70" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J70" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K70">
         <v>132</v>
@@ -7914,7 +7953,7 @@
         <v>26.51666667</v>
       </c>
       <c r="V70" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W70">
         <v>-0.010278</v>
@@ -7943,10 +7982,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C71" s="2">
         <v>45403.35449524305</v>
@@ -7964,13 +8003,13 @@
         <v>1277</v>
       </c>
       <c r="H71" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I71" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J71" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K71">
         <v>127</v>
@@ -7994,7 +8033,7 @@
         <v>27.23333333</v>
       </c>
       <c r="V71" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W71">
         <v>0.023889</v>
@@ -8023,10 +8062,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C72" s="2">
         <v>45403.35484331018</v>
@@ -8044,13 +8083,13 @@
         <v>1307</v>
       </c>
       <c r="H72" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I72" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J72" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K72">
         <v>149</v>
@@ -8074,7 +8113,7 @@
         <v>29.63333333</v>
       </c>
       <c r="V72" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W72">
         <v>0.08</v>
@@ -8103,10 +8142,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C73" s="2">
         <v>45403.35506581019</v>
@@ -8124,13 +8163,13 @@
         <v>1320</v>
       </c>
       <c r="H73" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I73" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J73" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K73">
         <v>144</v>
@@ -8166,7 +8205,7 @@
         <v>27.81666667</v>
       </c>
       <c r="V73" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W73">
         <v>-0.030278</v>
@@ -8195,10 +8234,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C74" s="2">
         <v>45403.3551937963</v>
@@ -8216,13 +8255,13 @@
         <v>1337</v>
       </c>
       <c r="H74" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I74" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J74" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K74">
         <v>146</v>
@@ -8246,7 +8285,7 @@
         <v>22.63333333</v>
       </c>
       <c r="V74" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W74">
         <v>-0.172778</v>
@@ -8275,10 +8314,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C75" s="2">
         <v>45403.35537799769</v>
@@ -8296,13 +8335,13 @@
         <v>1350</v>
       </c>
       <c r="H75" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I75" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J75" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K75">
         <v>138</v>
@@ -8338,7 +8377,7 @@
         <v>23.23333333</v>
       </c>
       <c r="V75" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W75">
         <v>0.02</v>
@@ -8367,10 +8406,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C76" s="2">
         <v>45403.35554219907</v>
@@ -8388,13 +8427,13 @@
         <v>1367</v>
       </c>
       <c r="H76" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I76" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J76" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K76">
         <v>145</v>
@@ -8418,7 +8457,7 @@
         <v>24.83333333</v>
       </c>
       <c r="V76" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W76">
         <v>0.053333</v>
@@ -8447,10 +8486,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C77" s="2">
         <v>45403.35576005787</v>
@@ -8468,13 +8507,13 @@
         <v>1380</v>
       </c>
       <c r="H77" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I77" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J77" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K77">
         <v>131</v>
@@ -8510,7 +8549,7 @@
         <v>25.86666667</v>
       </c>
       <c r="V77" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W77">
         <v>0.034444</v>
@@ -8539,10 +8578,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C78" s="2">
         <v>45403.35588299768</v>
@@ -8560,13 +8599,13 @@
         <v>1397</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I78" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J78" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K78">
         <v>136</v>
@@ -8590,7 +8629,7 @@
         <v>25.46666667</v>
       </c>
       <c r="V78" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W78">
         <v>-0.013333</v>
@@ -8619,10 +8658,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C79" s="2">
         <v>45403.35607357639</v>
@@ -8640,13 +8679,13 @@
         <v>1410</v>
       </c>
       <c r="H79" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I79" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J79" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K79">
         <v>128</v>
@@ -8682,7 +8721,7 @@
         <v>27.06666667</v>
       </c>
       <c r="V79" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W79">
         <v>0.053333</v>
@@ -8711,10 +8750,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C80" s="2">
         <v>45403.35623045139</v>
@@ -8732,13 +8771,13 @@
         <v>1427</v>
       </c>
       <c r="H80" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J80" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K80">
         <v>132</v>
@@ -8762,7 +8801,7 @@
         <v>26.6</v>
       </c>
       <c r="V80" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W80">
         <v>-0.015556</v>
@@ -8791,10 +8830,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C81" s="2">
         <v>45403.35657739583</v>
@@ -8812,13 +8851,13 @@
         <v>1457</v>
       </c>
       <c r="H81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I81" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J81" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K81">
         <v>110</v>
@@ -8842,7 +8881,7 @@
         <v>24.7</v>
       </c>
       <c r="V81" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W81">
         <v>-0.063333</v>
@@ -8871,10 +8910,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C82" s="2">
         <v>45403.35676763889</v>
@@ -8892,13 +8931,13 @@
         <v>1470</v>
       </c>
       <c r="H82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J82" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K82">
         <v>126</v>
@@ -8934,7 +8973,7 @@
         <v>25.78333333</v>
       </c>
       <c r="V82" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W82">
         <v>0.018056</v>
@@ -8963,10 +9002,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C83" s="2">
         <v>45403.35692618055</v>
@@ -8984,13 +9023,13 @@
         <v>1487</v>
       </c>
       <c r="H83" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I83" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J83" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K83">
         <v>123</v>
@@ -9014,7 +9053,7 @@
         <v>29.53333333</v>
       </c>
       <c r="V83" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W83">
         <v>0.125</v>
@@ -9043,10 +9082,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C84" s="2">
         <v>45403.3571484838</v>
@@ -9064,13 +9103,13 @@
         <v>1500</v>
       </c>
       <c r="H84" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I84" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J84" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K84">
         <v>125</v>
@@ -9106,7 +9145,7 @@
         <v>28.3</v>
       </c>
       <c r="V84" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W84">
         <v>-0.041111</v>
@@ -9135,10 +9174,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C85" s="2">
         <v>45403.35727391204</v>
@@ -9156,13 +9195,13 @@
         <v>1517</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I85" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J85" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K85">
         <v>122</v>
@@ -9186,7 +9225,7 @@
         <v>28.76666667</v>
       </c>
       <c r="V85" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W85">
         <v>0.015556</v>
@@ -9215,10 +9254,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C86" s="2">
         <v>45403.35746136574</v>
@@ -9236,13 +9275,13 @@
         <v>1530</v>
       </c>
       <c r="H86" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I86" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J86" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K86">
         <v>135</v>
@@ -9278,7 +9317,7 @@
         <v>28.76666667</v>
       </c>
       <c r="V86" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W86">
         <v>0</v>
@@ -9307,10 +9346,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C87" s="2">
         <v>45403.35762188657</v>
@@ -9328,13 +9367,13 @@
         <v>1547</v>
       </c>
       <c r="H87" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I87" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J87" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K87">
         <v>142</v>
@@ -9358,7 +9397,7 @@
         <v>26.8</v>
       </c>
       <c r="V87" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W87">
         <v>-0.065556</v>
@@ -9387,10 +9426,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C88" s="2">
         <v>45403.35796847222</v>
@@ -9408,13 +9447,13 @@
         <v>1577</v>
       </c>
       <c r="H88" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I88" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J88" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K88">
         <v>101</v>
@@ -9438,7 +9477,7 @@
         <v>23.3</v>
       </c>
       <c r="V88" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W88">
         <v>-0.116667</v>
@@ -9467,10 +9506,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C89" s="2">
         <v>45403.35831515046</v>
@@ -9488,13 +9527,13 @@
         <v>1607</v>
       </c>
       <c r="H89" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I89" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J89" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K89">
         <v>120</v>
@@ -9518,7 +9557,7 @@
         <v>27.23333333</v>
       </c>
       <c r="V89" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W89">
         <v>0.131111</v>
@@ -9547,10 +9586,10 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C90" s="2">
         <v>45403.35853854167</v>
@@ -9568,13 +9607,13 @@
         <v>1620</v>
       </c>
       <c r="H90" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I90" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J90" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K90">
         <v>113</v>
@@ -9610,7 +9649,7 @@
         <v>25.22222222</v>
       </c>
       <c r="V90" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W90">
         <v>-0.022346</v>
@@ -9639,10 +9678,10 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C91" s="2">
         <v>45403.35866368056</v>
@@ -9660,13 +9699,13 @@
         <v>1637</v>
       </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I91" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J91" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K91">
         <v>105</v>
@@ -9690,7 +9729,7 @@
         <v>23.63333333</v>
       </c>
       <c r="V91" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W91">
         <v>-0.052963</v>
@@ -9719,10 +9758,10 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C92" s="2">
         <v>45403.35935561343</v>
@@ -9740,13 +9779,13 @@
         <v>1697</v>
       </c>
       <c r="H92" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I92" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J92" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K92">
         <v>122</v>
@@ -9770,7 +9809,7 @@
         <v>22.96666667</v>
       </c>
       <c r="V92" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W92">
         <v>-0.011111</v>
@@ -9799,10 +9838,10 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C93" s="2">
         <v>45403.35970369213</v>
@@ -9820,13 +9859,13 @@
         <v>1727</v>
       </c>
       <c r="H93" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I93" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J93" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K93">
         <v>103</v>
@@ -9850,7 +9889,7 @@
         <v>24.6</v>
       </c>
       <c r="V93" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W93">
         <v>0.054444</v>
@@ -9879,10 +9918,10 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C94" s="2">
         <v>45403.35992748843</v>
@@ -9900,13 +9939,13 @@
         <v>1740</v>
       </c>
       <c r="H94" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J94" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K94">
         <v>118</v>
@@ -9942,7 +9981,7 @@
         <v>23.11666667</v>
       </c>
       <c r="V94" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W94">
         <v>-0.012361</v>
@@ -9971,10 +10010,10 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C95" s="2">
         <v>45403.3600502199</v>
@@ -9992,13 +10031,13 @@
         <v>1757</v>
       </c>
       <c r="H95" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I95" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J95" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K95">
         <v>96</v>
@@ -10022,7 +10061,7 @@
         <v>20.8</v>
       </c>
       <c r="V95" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W95">
         <v>-0.077222</v>
@@ -10051,10 +10090,10 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C96" s="2">
         <v>45403.36039835648</v>
@@ -10072,13 +10111,13 @@
         <v>1787</v>
       </c>
       <c r="H96" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I96" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J96" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K96">
         <v>101</v>
@@ -10102,7 +10141,7 @@
         <v>24.7</v>
       </c>
       <c r="V96" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W96">
         <v>0.13</v>
@@ -10131,10 +10170,10 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C97" s="2">
         <v>45403.36062178241</v>
@@ -10152,13 +10191,13 @@
         <v>1800</v>
       </c>
       <c r="H97" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I97" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J97" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="K97">
         <v>121</v>
@@ -10194,7 +10233,7 @@
         <v>22.88333333</v>
       </c>
       <c r="V97" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W97">
         <v>-0.030278</v>
@@ -10223,10 +10262,10 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C98" s="2">
         <v>45403.36074664352</v>
@@ -10244,13 +10283,13 @@
         <v>1817</v>
       </c>
       <c r="H98" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I98" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J98" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K98">
         <v>96</v>
@@ -10274,7 +10313,7 @@
         <v>21.76666667</v>
       </c>
       <c r="V98" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W98">
         <v>-0.037222</v>
@@ -10303,10 +10342,10 @@
     </row>
     <row r="99" spans="1:30">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C99" s="2">
         <v>45403.36109293981</v>
@@ -10324,13 +10363,13 @@
         <v>1847</v>
       </c>
       <c r="H99" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I99" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J99" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K99">
         <v>82</v>
@@ -10354,7 +10393,7 @@
         <v>26.13333333</v>
       </c>
       <c r="V99" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W99">
         <v>0.145556</v>
@@ -10383,10 +10422,10 @@
     </row>
     <row r="100" spans="1:30">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C100" s="2">
         <v>45403.36144085648</v>
@@ -10404,13 +10443,13 @@
         <v>1877</v>
       </c>
       <c r="H100" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J100" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K100">
         <v>100</v>
@@ -10434,7 +10473,7 @@
         <v>23.86666667</v>
       </c>
       <c r="V100" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W100">
         <v>-0.075556</v>
@@ -10463,10 +10502,10 @@
     </row>
     <row r="101" spans="1:30">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C101" s="2">
         <v>45403.36178607639</v>
@@ -10484,13 +10523,13 @@
         <v>1907</v>
       </c>
       <c r="H101" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J101" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K101">
         <v>99</v>
@@ -10514,7 +10553,7 @@
         <v>18.03333333</v>
       </c>
       <c r="V101" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W101">
         <v>-0.194444</v>
@@ -10543,10 +10582,10 @@
     </row>
     <row r="102" spans="1:30">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C102" s="2">
         <v>45403.36213509259</v>
@@ -10564,13 +10603,13 @@
         <v>1937</v>
       </c>
       <c r="H102" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I102" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J102" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="K102">
         <v>104</v>
@@ -10594,7 +10633,7 @@
         <v>20.56666667</v>
       </c>
       <c r="V102" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W102">
         <v>0.08444400000000001</v>
@@ -10623,10 +10662,10 @@
     </row>
     <row r="103" spans="1:30">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C103" s="2">
         <v>45403.36248055556</v>
@@ -10644,13 +10683,13 @@
         <v>1967</v>
       </c>
       <c r="H103" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I103" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="J103" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K103">
         <v>144</v>
@@ -10674,7 +10713,7 @@
         <v>22.2</v>
       </c>
       <c r="V103" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W103">
         <v>0.054444</v>
@@ -10703,10 +10742,10 @@
     </row>
     <row r="104" spans="1:30">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C104" s="2">
         <v>45403.36282774305</v>
@@ -10724,13 +10763,13 @@
         <v>1997</v>
       </c>
       <c r="H104" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I104" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J104" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K104">
         <v>143</v>
@@ -10754,7 +10793,7 @@
         <v>15.86666667</v>
       </c>
       <c r="V104" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W104">
         <v>-0.211111</v>
@@ -10783,10 +10822,10 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C105" s="2">
         <v>45403.36317440972</v>
@@ -10804,13 +10843,13 @@
         <v>2027</v>
       </c>
       <c r="H105" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I105" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J105" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K105">
         <v>147</v>
@@ -10834,7 +10873,7 @@
         <v>16.63333333</v>
       </c>
       <c r="V105" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W105">
         <v>0.025556</v>
@@ -10863,10 +10902,10 @@
     </row>
     <row r="106" spans="1:30">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C106" s="2">
         <v>45403.36352231482</v>
@@ -10884,13 +10923,13 @@
         <v>2057</v>
       </c>
       <c r="H106" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I106" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J106" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K106">
         <v>130</v>
@@ -10914,7 +10953,7 @@
         <v>16.83333333</v>
       </c>
       <c r="V106" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W106">
         <v>0.006667</v>
@@ -10943,10 +10982,10 @@
     </row>
     <row r="107" spans="1:30">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C107" s="2">
         <v>45403.36421915509</v>
@@ -10964,13 +11003,13 @@
         <v>2117</v>
       </c>
       <c r="H107" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I107" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J107" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K107">
         <v>129</v>
@@ -10994,7 +11033,7 @@
         <v>18.91666667</v>
       </c>
       <c r="V107" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W107">
         <v>0.034722</v>
@@ -11023,10 +11062,10 @@
     </row>
     <row r="108" spans="1:30">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C108" s="2">
         <v>45403.36440714121</v>
@@ -11044,13 +11083,13 @@
         <v>2130</v>
       </c>
       <c r="H108" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I108" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J108" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K108">
         <v>123</v>
@@ -11086,7 +11125,7 @@
         <v>19.90909091</v>
       </c>
       <c r="V108" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W108">
         <v>0.003007</v>
@@ -11115,10 +11154,10 @@
     </row>
     <row r="109" spans="1:30">
       <c r="A109" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C109" s="2">
         <v>45403.36456484954</v>
@@ -11136,13 +11175,13 @@
         <v>2147</v>
       </c>
       <c r="H109" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I109" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J109" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K109">
         <v>110</v>
@@ -11166,7 +11205,7 @@
         <v>20.66666667</v>
       </c>
       <c r="V109" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W109">
         <v>0.025253</v>
@@ -11195,10 +11234,10 @@
     </row>
     <row r="110" spans="1:30">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C110" s="2">
         <v>45403.36491126157</v>
@@ -11216,13 +11255,13 @@
         <v>2177</v>
       </c>
       <c r="H110" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I110" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J110" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K110">
         <v>117</v>
@@ -11246,7 +11285,7 @@
         <v>21.13333333</v>
       </c>
       <c r="V110" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W110">
         <v>0.015556</v>
@@ -11275,10 +11314,10 @@
     </row>
     <row r="111" spans="1:30">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C111" s="2">
         <v>45403.36560518519</v>
@@ -11296,13 +11335,13 @@
         <v>2237</v>
       </c>
       <c r="H111" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I111" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J111" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K111">
         <v>142</v>
@@ -11326,7 +11365,7 @@
         <v>20.88333333</v>
       </c>
       <c r="V111" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W111">
         <v>-0.004167</v>
@@ -11355,10 +11394,10 @@
     </row>
     <row r="112" spans="1:30">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C112" s="2">
         <v>45403.36579548611</v>
@@ -11376,13 +11415,13 @@
         <v>2250</v>
       </c>
       <c r="H112" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I112" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J112" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K112">
         <v>114</v>
@@ -11418,7 +11457,7 @@
         <v>21.13333333</v>
       </c>
       <c r="V112" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W112">
         <v>0.002083</v>
@@ -11447,10 +11486,10 @@
     </row>
     <row r="113" spans="1:30">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C113" s="2">
         <v>45403.3663000926</v>
@@ -11468,13 +11507,13 @@
         <v>2297</v>
       </c>
       <c r="H113" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I113" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J113" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K113">
         <v>141</v>
@@ -11498,7 +11537,7 @@
         <v>20.51666667</v>
       </c>
       <c r="V113" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W113">
         <v>-0.010278</v>
@@ -11527,10 +11566,10 @@
     </row>
     <row r="114" spans="1:30">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C114" s="2">
         <v>45403.36648957176</v>
@@ -11548,13 +11587,13 @@
         <v>2310</v>
       </c>
       <c r="H114" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J114" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K114">
         <v>111</v>
@@ -11590,7 +11629,7 @@
         <v>19.58333333</v>
       </c>
       <c r="V114" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W114">
         <v>-0.015556</v>
@@ -11619,10 +11658,10 @@
     </row>
     <row r="115" spans="1:30">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C115" s="2">
         <v>45403.36718447917</v>
@@ -11640,13 +11679,13 @@
         <v>2370</v>
       </c>
       <c r="H115" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I115" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J115" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K115">
         <v>127</v>
@@ -11682,7 +11721,7 @@
         <v>23.81666667</v>
       </c>
       <c r="V115" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W115">
         <v>0.07055599999999999</v>
@@ -11711,10 +11750,10 @@
     </row>
     <row r="116" spans="1:30">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C116" s="2">
         <v>45403.36756590278</v>
@@ -11732,13 +11771,13 @@
         <v>2400</v>
       </c>
       <c r="H116" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I116" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J116" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K116">
         <v>119</v>
@@ -11774,7 +11813,7 @@
         <v>20.93333333</v>
       </c>
       <c r="V116" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W116">
         <v>-0.096111</v>
@@ -11803,10 +11842,10 @@
     </row>
     <row r="117" spans="1:30">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C117" s="2">
         <v>45403.36787876157</v>
@@ -11824,13 +11863,13 @@
         <v>2430</v>
       </c>
       <c r="H117" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I117" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J117" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K117">
         <v>129</v>
@@ -11866,7 +11905,7 @@
         <v>19.76666667</v>
       </c>
       <c r="V117" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W117">
         <v>-0.038889</v>
@@ -11895,10 +11934,10 @@
     </row>
     <row r="118" spans="1:30">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C118" s="2">
         <v>45403.368385</v>
@@ -11916,13 +11955,13 @@
         <v>2477</v>
       </c>
       <c r="H118" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I118" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J118" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K118">
         <v>111</v>
@@ -11946,7 +11985,7 @@
         <v>21.21666667</v>
       </c>
       <c r="V118" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W118">
         <v>0.008056000000000001</v>
@@ -11975,10 +12014,10 @@
     </row>
     <row r="119" spans="1:30">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C119" s="2">
         <v>45403.36908070602</v>
@@ -11996,13 +12035,13 @@
         <v>2537</v>
       </c>
       <c r="H119" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I119" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J119" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K119">
         <v>80</v>
@@ -12026,7 +12065,7 @@
         <v>22.31666667</v>
       </c>
       <c r="V119" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W119">
         <v>0.018333</v>
@@ -12055,10 +12094,10 @@
     </row>
     <row r="120" spans="1:30">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C120" s="2">
         <v>45403.36942525463</v>
@@ -12076,13 +12115,13 @@
         <v>2567</v>
       </c>
       <c r="H120" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I120" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J120" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K120">
         <v>40</v>
@@ -12106,7 +12145,7 @@
         <v>29.3</v>
       </c>
       <c r="V120" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W120">
         <v>0.232778</v>
@@ -12135,10 +12174,10 @@
     </row>
     <row r="121" spans="1:30">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C121" s="2">
         <v>45403.37046804398</v>
@@ -12156,13 +12195,13 @@
         <v>2657</v>
       </c>
       <c r="H121" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I121" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J121" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="K121">
         <v>119</v>
@@ -12186,7 +12225,7 @@
         <v>26.8</v>
       </c>
       <c r="V121" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W121">
         <v>-0.027778</v>
@@ -12215,10 +12254,10 @@
     </row>
     <row r="122" spans="1:30">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C122" s="2">
         <v>45403.37116125</v>
@@ -12236,13 +12275,13 @@
         <v>2717</v>
       </c>
       <c r="H122" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J122" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K122">
         <v>128</v>
@@ -12266,7 +12305,7 @@
         <v>19.95</v>
       </c>
       <c r="V122" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W122">
         <v>-0.114167</v>
@@ -12295,10 +12334,10 @@
     </row>
     <row r="123" spans="1:30">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C123" s="2">
         <v>45403.37151903935</v>
@@ -12316,13 +12355,13 @@
         <v>2747</v>
       </c>
       <c r="H123" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I123" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J123" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K123">
         <v>158</v>
@@ -12346,7 +12385,7 @@
         <v>19.26666667</v>
       </c>
       <c r="V123" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W123">
         <v>-0.022778</v>
@@ -12375,10 +12414,10 @@
     </row>
     <row r="124" spans="1:30">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C124" s="2">
         <v>45403.3732447338</v>
@@ -12396,13 +12435,13 @@
         <v>2897</v>
       </c>
       <c r="H124" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I124" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J124" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K124">
         <v>81</v>
@@ -12426,7 +12465,7 @@
         <v>19.55333333</v>
       </c>
       <c r="V124" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W124">
         <v>0.001911</v>
@@ -12455,10 +12494,10 @@
     </row>
     <row r="125" spans="1:30">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C125" s="2">
         <v>45403.37463532407</v>
@@ -12476,13 +12515,13 @@
         <v>3017</v>
       </c>
       <c r="H125" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I125" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J125" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K125">
         <v>91</v>
@@ -12506,7 +12545,7 @@
         <v>19.60833333</v>
       </c>
       <c r="V125" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W125">
         <v>0.000458</v>
@@ -12535,10 +12574,10 @@
     </row>
     <row r="126" spans="1:30">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C126" s="2">
         <v>45403.3760225463</v>
@@ -12556,13 +12595,13 @@
         <v>3137</v>
       </c>
       <c r="H126" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I126" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J126" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K126">
         <v>162</v>
@@ -12586,7 +12625,7 @@
         <v>20.91666667</v>
       </c>
       <c r="V126" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W126">
         <v>0.010903</v>
@@ -12615,10 +12654,10 @@
     </row>
     <row r="127" spans="1:30">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C127" s="2">
         <v>45403.37741244213</v>
@@ -12636,13 +12675,13 @@
         <v>3257</v>
       </c>
       <c r="H127" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I127" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J127" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K127">
         <v>101</v>
@@ -12666,7 +12705,7 @@
         <v>19.225</v>
       </c>
       <c r="V127" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W127">
         <v>-0.014097</v>
@@ -12695,10 +12734,10 @@
     </row>
     <row r="128" spans="1:30">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C128" s="2">
         <v>45403.37879991898</v>
@@ -12716,13 +12755,13 @@
         <v>3377</v>
       </c>
       <c r="H128" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I128" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J128" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K128">
         <v>346</v>
@@ -12746,7 +12785,7 @@
         <v>21.98333333</v>
       </c>
       <c r="V128" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W128">
         <v>0.022986</v>
@@ -12775,10 +12814,10 @@
     </row>
     <row r="129" spans="1:30">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C129" s="2">
         <v>45403.37914791667</v>
@@ -12796,13 +12835,13 @@
         <v>3407</v>
       </c>
       <c r="H129" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I129" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J129" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="K129">
         <v>314</v>
@@ -12826,7 +12865,7 @@
         <v>19.13333333</v>
       </c>
       <c r="V129" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W129">
         <v>-0.095</v>
@@ -12855,10 +12894,10 @@
     </row>
     <row r="130" spans="1:30">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C130" s="2">
         <v>45403.38018886574</v>
@@ -12876,13 +12915,13 @@
         <v>3497</v>
       </c>
       <c r="H130" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I130" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J130" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K130">
         <v>96</v>
@@ -12906,7 +12945,7 @@
         <v>19</v>
       </c>
       <c r="V130" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W130">
         <v>-0.001481</v>
@@ -12935,10 +12974,10 @@
     </row>
     <row r="131" spans="1:30">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C131" s="2">
         <v>45403.38053690972</v>
@@ -12956,13 +12995,13 @@
         <v>3527</v>
       </c>
       <c r="H131" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I131" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J131" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="K131">
         <v>121</v>
@@ -12986,7 +13025,7 @@
         <v>19.46666667</v>
       </c>
       <c r="V131" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W131">
         <v>0.015556</v>
@@ -13015,10 +13054,10 @@
     </row>
     <row r="132" spans="1:30">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C132" s="2">
         <v>45403.38088469907</v>
@@ -13036,13 +13075,13 @@
         <v>3557</v>
       </c>
       <c r="H132" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I132" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J132" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="K132">
         <v>352</v>
@@ -13066,7 +13105,7 @@
         <v>21</v>
       </c>
       <c r="V132" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W132">
         <v>0.051111</v>
@@ -13095,10 +13134,10 @@
     </row>
     <row r="133" spans="1:30">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C133" s="2">
         <v>45403.3815791088</v>
@@ -13116,13 +13155,13 @@
         <v>3617</v>
       </c>
       <c r="H133" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I133" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J133" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K133">
         <v>92</v>
@@ -13146,7 +13185,7 @@
         <v>18.31666667</v>
       </c>
       <c r="V133" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W133">
         <v>-0.044722</v>
@@ -13175,10 +13214,10 @@
     </row>
     <row r="134" spans="1:30">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C134" s="2">
         <v>45403.38192587963</v>
@@ -13196,13 +13235,13 @@
         <v>3647</v>
       </c>
       <c r="H134" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I134" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J134" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K134">
         <v>94</v>
@@ -13226,7 +13265,7 @@
         <v>19.46666667</v>
       </c>
       <c r="V134" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W134">
         <v>0.038333</v>
@@ -13255,10 +13294,10 @@
     </row>
     <row r="135" spans="1:30">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C135" s="2">
         <v>45403.38227145834</v>
@@ -13276,13 +13315,13 @@
         <v>3677</v>
       </c>
       <c r="H135" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I135" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J135" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="K135">
         <v>116</v>
@@ -13306,7 +13345,7 @@
         <v>19.13333333</v>
       </c>
       <c r="V135" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W135">
         <v>-0.011111</v>
@@ -13335,10 +13374,10 @@
     </row>
     <row r="136" spans="1:30">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C136" s="2">
         <v>45403.38296587963</v>
@@ -13356,13 +13395,13 @@
         <v>3737</v>
       </c>
       <c r="H136" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I136" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J136" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="K136">
         <v>129</v>
@@ -13386,7 +13425,7 @@
         <v>19.36666667</v>
       </c>
       <c r="V136" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W136">
         <v>0.003889</v>
@@ -13415,10 +13454,10 @@
     </row>
     <row r="137" spans="1:30">
       <c r="A137" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C137" s="2">
         <v>45403.38331354166</v>
@@ -13436,13 +13475,13 @@
         <v>3767</v>
       </c>
       <c r="H137" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I137" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J137" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="K137">
         <v>193</v>
@@ -13466,7 +13505,7 @@
         <v>19.8</v>
       </c>
       <c r="V137" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W137">
         <v>0.014444</v>
@@ -13495,10 +13534,10 @@
     </row>
     <row r="138" spans="1:30">
       <c r="A138" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C138" s="2">
         <v>45403.38366085648</v>
@@ -13516,13 +13555,13 @@
         <v>3797</v>
       </c>
       <c r="H138" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I138" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J138" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K138">
         <v>103</v>
@@ -13546,7 +13585,7 @@
         <v>19.66666667</v>
       </c>
       <c r="V138" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W138">
         <v>-0.004444</v>
@@ -13575,10 +13614,10 @@
     </row>
     <row r="139" spans="1:30">
       <c r="A139" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C139" s="2">
         <v>45403.384008125</v>
@@ -13596,13 +13635,13 @@
         <v>3827</v>
       </c>
       <c r="H139" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I139" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J139" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K139">
         <v>104</v>
@@ -13626,7 +13665,7 @@
         <v>18.83333333</v>
       </c>
       <c r="V139" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W139">
         <v>-0.027778</v>
@@ -13655,10 +13694,10 @@
     </row>
     <row r="140" spans="1:30">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C140" s="2">
         <v>45403.38435752315</v>
@@ -13676,13 +13715,13 @@
         <v>3857</v>
       </c>
       <c r="H140" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I140" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J140" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="K140">
         <v>152</v>
@@ -13706,7 +13745,7 @@
         <v>2.73333333</v>
       </c>
       <c r="V140" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W140">
         <v>-0.536667</v>
@@ -13745,102 +13784,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2">
         <v>45403.38470376157</v>
@@ -13858,13 +13897,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K2">
         <v>139</v>
@@ -13888,7 +13927,7 @@
         <v>-93.3</v>
       </c>
       <c r="V2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="X2">
         <v>-93.3</v>
@@ -13899,10 +13938,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>45403.38505405092</v>
@@ -13920,13 +13959,13 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J3" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K3">
         <v>46</v>
@@ -13950,7 +13989,7 @@
         <v>-92.53333333</v>
       </c>
       <c r="V3" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W3">
         <v>0.025556</v>
@@ -13973,10 +14012,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2">
         <v>45403.38540138889</v>
@@ -13994,13 +14033,13 @@
         <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I4" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J4" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K4">
         <v>14</v>
@@ -14024,7 +14063,7 @@
         <v>-89.03333333</v>
       </c>
       <c r="V4" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W4">
         <v>0.116667</v>
@@ -14053,10 +14092,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>45403.38574840278</v>
@@ -14074,13 +14113,13 @@
         <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I5" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J5" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="K5">
         <v>136</v>
@@ -14104,7 +14143,7 @@
         <v>-82.7</v>
       </c>
       <c r="V5" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W5">
         <v>0.211111</v>
@@ -14133,10 +14172,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2">
         <v>45403.38609175926</v>
@@ -14154,13 +14193,13 @@
         <v>120</v>
       </c>
       <c r="H6" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I6" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J6" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K6">
         <v>113</v>
@@ -14184,7 +14223,7 @@
         <v>-82</v>
       </c>
       <c r="V6" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W6">
         <v>0.023333</v>
@@ -14213,10 +14252,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>45403.38678726852</v>
@@ -14234,13 +14273,13 @@
         <v>180</v>
       </c>
       <c r="H7" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I7" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J7" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K7">
         <v>273</v>
@@ -14264,7 +14303,7 @@
         <v>-73.40000000000001</v>
       </c>
       <c r="V7" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W7">
         <v>0.143333</v>
@@ -14293,10 +14332,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2">
         <v>45403.38713508102</v>
@@ -14314,13 +14353,13 @@
         <v>210</v>
       </c>
       <c r="H8" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I8" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J8" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="K8">
         <v>110</v>
@@ -14344,7 +14383,7 @@
         <v>-69</v>
       </c>
       <c r="V8" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W8">
         <v>0.146667</v>
@@ -14373,10 +14412,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2">
         <v>45403.38748087963</v>
@@ -14394,13 +14433,13 @@
         <v>240</v>
       </c>
       <c r="H9" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I9" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J9" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K9">
         <v>145</v>
@@ -14424,7 +14463,7 @@
         <v>-65.3</v>
       </c>
       <c r="V9" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W9">
         <v>0.123333</v>
@@ -14453,10 +14492,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v>45403.38817590278</v>
@@ -14474,13 +14513,13 @@
         <v>300</v>
       </c>
       <c r="H10" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I10" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J10" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K10">
         <v>36</v>
@@ -14504,7 +14543,7 @@
         <v>-54.85</v>
       </c>
       <c r="V10" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W10">
         <v>0.174167</v>
@@ -14533,10 +14572,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2">
         <v>45403.38852355324</v>
@@ -14554,13 +14593,13 @@
         <v>330</v>
       </c>
       <c r="H11" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I11" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J11" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K11">
         <v>47</v>
@@ -14584,7 +14623,7 @@
         <v>-46.06666667</v>
       </c>
       <c r="V11" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W11">
         <v>0.292778</v>
@@ -14613,10 +14652,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2">
         <v>45403.3888712037</v>
@@ -14634,13 +14673,13 @@
         <v>360</v>
       </c>
       <c r="H12" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I12" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="J12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="K12">
         <v>139</v>
@@ -14664,7 +14703,7 @@
         <v>-44.83333333</v>
       </c>
       <c r="V12" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W12">
         <v>0.041111</v>
@@ -14693,10 +14732,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2">
         <v>45403.38921841436</v>
@@ -14714,13 +14753,13 @@
         <v>390</v>
       </c>
       <c r="H13" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I13" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J13" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K13">
         <v>147</v>
@@ -14744,7 +14783,7 @@
         <v>-44.4</v>
       </c>
       <c r="V13" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W13">
         <v>0.014444</v>
@@ -14773,10 +14812,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C14" s="2">
         <v>45403.3895640625</v>
@@ -14794,13 +14833,13 @@
         <v>420</v>
       </c>
       <c r="H14" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I14" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J14" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="K14">
         <v>129</v>
@@ -14824,7 +14863,7 @@
         <v>-42.9</v>
       </c>
       <c r="V14" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W14">
         <v>0.05</v>
@@ -14853,10 +14892,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>45403.38991324074</v>
@@ -14874,13 +14913,13 @@
         <v>450</v>
       </c>
       <c r="H15" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I15" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J15" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K15">
         <v>126</v>
@@ -14904,7 +14943,7 @@
         <v>-44.06666667</v>
       </c>
       <c r="V15" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W15">
         <v>-0.038889</v>
@@ -14933,10 +14972,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2">
         <v>45403.39025761574</v>
@@ -14954,13 +14993,13 @@
         <v>480</v>
       </c>
       <c r="H16" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I16" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="J16" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="K16">
         <v>122</v>
@@ -14984,7 +15023,7 @@
         <v>-42.1</v>
       </c>
       <c r="V16" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W16">
         <v>0.065556</v>
@@ -15013,10 +15052,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2">
         <v>45403.39048606482</v>
@@ -15034,13 +15073,13 @@
         <v>493</v>
       </c>
       <c r="H17" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J17" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K17">
         <v>139</v>
@@ -15076,7 +15115,7 @@
         <v>-2.33589744</v>
       </c>
       <c r="V17" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W17">
         <v>0.020392</v>
@@ -15105,10 +15144,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2">
         <v>45403.39060597222</v>
@@ -15126,13 +15165,13 @@
         <v>510</v>
       </c>
       <c r="H18" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I18" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="J18" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="K18">
         <v>103</v>
@@ -15156,7 +15195,7 @@
         <v>-38.93333333</v>
       </c>
       <c r="V18" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W18">
         <v>-1.219915</v>
@@ -15185,10 +15224,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2">
         <v>45403.39095601852</v>
@@ -15206,13 +15245,13 @@
         <v>540</v>
       </c>
       <c r="H19" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I19" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="J19" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K19">
         <v>135</v>
@@ -15236,7 +15275,7 @@
         <v>-38.5</v>
       </c>
       <c r="V19" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W19">
         <v>0.014444</v>
@@ -15265,10 +15304,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2">
         <v>45403.39130103009</v>
@@ -15286,13 +15325,13 @@
         <v>570</v>
       </c>
       <c r="H20" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I20" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="J20" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K20">
         <v>84</v>
@@ -15316,7 +15355,7 @@
         <v>-36.76666667</v>
       </c>
       <c r="V20" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W20">
         <v>0.057778</v>
@@ -15345,10 +15384,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2">
         <v>45403.39199434028</v>
@@ -15366,13 +15405,13 @@
         <v>630</v>
       </c>
       <c r="H21" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I21" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="J21" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K21">
         <v>115</v>
@@ -15396,7 +15435,7 @@
         <v>-35.76666667</v>
       </c>
       <c r="V21" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W21">
         <v>0.016667</v>
@@ -15425,10 +15464,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>45403.39234143519</v>
@@ -15446,13 +15485,13 @@
         <v>660</v>
       </c>
       <c r="H22" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I22" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="J22" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="K22">
         <v>109</v>
@@ -15476,7 +15515,7 @@
         <v>-34.43333333</v>
       </c>
       <c r="V22" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W22">
         <v>0.044444</v>
@@ -15505,10 +15544,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>45403.39303620371</v>
@@ -15526,13 +15565,13 @@
         <v>720</v>
       </c>
       <c r="H23" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I23" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J23" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="K23">
         <v>109</v>
@@ -15556,7 +15595,7 @@
         <v>-31.71666667</v>
       </c>
       <c r="V23" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W23">
         <v>0.045278</v>
@@ -15585,10 +15624,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2">
         <v>45403.39338446759</v>
@@ -15606,13 +15645,13 @@
         <v>750</v>
       </c>
       <c r="H24" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I24" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="J24" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K24">
         <v>96</v>
@@ -15636,7 +15675,7 @@
         <v>-30.96666667</v>
       </c>
       <c r="V24" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W24">
         <v>0.025</v>
@@ -15665,10 +15704,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2">
         <v>45403.39357175926</v>
@@ -15686,13 +15725,13 @@
         <v>763</v>
       </c>
       <c r="H25" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I25" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J25" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K25">
         <v>107</v>
@@ -15728,7 +15767,7 @@
         <v>-34.5962963</v>
       </c>
       <c r="V25" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W25">
         <v>-0.013443</v>
@@ -15757,10 +15796,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2">
         <v>45403.39407809028</v>
@@ -15778,13 +15817,13 @@
         <v>810</v>
       </c>
       <c r="H26" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I26" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="J26" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="K26">
         <v>133</v>
@@ -15808,7 +15847,7 @@
         <v>-30.46666667</v>
       </c>
       <c r="V26" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W26">
         <v>0.068827</v>
@@ -15837,10 +15876,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
         <v>45403.39442841435</v>
@@ -15858,13 +15897,13 @@
         <v>840</v>
       </c>
       <c r="H27" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I27" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="J27" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K27">
         <v>127</v>
@@ -15888,7 +15927,7 @@
         <v>-29.83333333</v>
       </c>
       <c r="V27" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W27">
         <v>0.021111</v>
@@ -15917,10 +15956,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>45403.39511917824</v>
@@ -15938,13 +15977,13 @@
         <v>900</v>
       </c>
       <c r="H28" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I28" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J28" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="K28">
         <v>105</v>
@@ -15968,7 +16007,7 @@
         <v>-28.93333333</v>
       </c>
       <c r="V28" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W28">
         <v>0.015</v>
@@ -15997,10 +16036,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2">
         <v>45403.39546671297</v>
@@ -16018,13 +16057,13 @@
         <v>930</v>
       </c>
       <c r="H29" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I29" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J29" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K29">
         <v>118</v>
@@ -16048,7 +16087,7 @@
         <v>-27.9</v>
       </c>
       <c r="V29" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W29">
         <v>0.034444</v>
@@ -16077,10 +16116,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2">
         <v>45403.39616402778</v>
@@ -16098,13 +16137,13 @@
         <v>990</v>
       </c>
       <c r="H30" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I30" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J30" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K30">
         <v>122</v>
@@ -16128,7 +16167,7 @@
         <v>-25.65</v>
       </c>
       <c r="V30" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W30">
         <v>0.0375</v>
@@ -16157,10 +16196,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>45403.3965112037</v>
@@ -16178,13 +16217,13 @@
         <v>1020</v>
       </c>
       <c r="H31" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I31" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J31" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="K31">
         <v>111</v>
@@ -16208,7 +16247,7 @@
         <v>-24.93333333</v>
       </c>
       <c r="V31" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W31">
         <v>0.023889</v>
@@ -16237,10 +16276,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2">
         <v>45403.39720318287</v>
@@ -16258,13 +16297,13 @@
         <v>1080</v>
       </c>
       <c r="H32" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I32" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J32" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K32">
         <v>111</v>
@@ -16288,7 +16327,7 @@
         <v>-24.33333333</v>
       </c>
       <c r="V32" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W32">
         <v>0.01</v>
@@ -16317,10 +16356,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2">
         <v>45403.39755100694</v>
@@ -16338,13 +16377,13 @@
         <v>1110</v>
       </c>
       <c r="H33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I33" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J33" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K33">
         <v>126</v>
@@ -16368,7 +16407,7 @@
         <v>-23.63333333</v>
       </c>
       <c r="V33" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W33">
         <v>0.023333</v>
@@ -16397,10 +16436,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2">
         <v>45403.39789850695</v>
@@ -16418,13 +16457,13 @@
         <v>1140</v>
       </c>
       <c r="H34" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I34" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="J34" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K34">
         <v>141</v>
@@ -16448,7 +16487,7 @@
         <v>-22.96666667</v>
       </c>
       <c r="V34" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W34">
         <v>0.022222</v>
@@ -16477,10 +16516,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2">
         <v>45403.39824560185</v>
@@ -16498,13 +16537,13 @@
         <v>1170</v>
       </c>
       <c r="H35" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I35" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J35" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K35">
         <v>140</v>
@@ -16528,7 +16567,7 @@
         <v>-23.3</v>
       </c>
       <c r="V35" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W35">
         <v>-0.011111</v>
@@ -16557,10 +16596,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2">
         <v>45403.39859101852</v>
@@ -16578,13 +16617,13 @@
         <v>1200</v>
       </c>
       <c r="H36" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I36" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="J36" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="K36">
         <v>127</v>
@@ -16608,7 +16647,7 @@
         <v>-23.73333333</v>
       </c>
       <c r="V36" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W36">
         <v>-0.014444</v>
@@ -16637,10 +16676,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2">
         <v>45403.3989393287</v>
@@ -16658,13 +16697,13 @@
         <v>1230</v>
       </c>
       <c r="H37" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I37" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="J37" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K37">
         <v>137</v>
@@ -16688,7 +16727,7 @@
         <v>-23.3</v>
       </c>
       <c r="V37" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W37">
         <v>0.014444</v>
@@ -16717,10 +16756,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2">
         <v>45403.39928760417</v>
@@ -16738,13 +16777,13 @@
         <v>1260</v>
       </c>
       <c r="H38" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I38" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="J38" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="K38">
         <v>141</v>
@@ -16768,7 +16807,7 @@
         <v>-23.4</v>
       </c>
       <c r="V38" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W38">
         <v>-0.003333</v>
@@ -16797,10 +16836,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>45403.39963373842</v>
@@ -16818,13 +16857,13 @@
         <v>1290</v>
       </c>
       <c r="H39" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I39" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J39" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K39">
         <v>143</v>
@@ -16848,7 +16887,7 @@
         <v>-22.96666667</v>
       </c>
       <c r="V39" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W39">
         <v>0.014444</v>
@@ -16877,10 +16916,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2">
         <v>45403.39998326389</v>
@@ -16898,13 +16937,13 @@
         <v>1320</v>
       </c>
       <c r="H40" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I40" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="J40" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="K40">
         <v>143</v>
@@ -16928,7 +16967,7 @@
         <v>-22.1</v>
       </c>
       <c r="V40" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W40">
         <v>0.028889</v>
@@ -16957,10 +16996,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C41" s="2">
         <v>45403.40032832176</v>
@@ -16978,13 +17017,13 @@
         <v>1350</v>
       </c>
       <c r="H41" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I41" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J41" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="K41">
         <v>142</v>
@@ -17008,7 +17047,7 @@
         <v>-21.43333333</v>
       </c>
       <c r="V41" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W41">
         <v>0.022222</v>
@@ -17037,10 +17076,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2">
         <v>45403.40067550926</v>
@@ -17058,13 +17097,13 @@
         <v>1380</v>
       </c>
       <c r="H42" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I42" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J42" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K42">
         <v>140</v>
@@ -17088,7 +17127,7 @@
         <v>-21.33333333</v>
       </c>
       <c r="V42" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W42">
         <v>0.003333</v>
@@ -17117,10 +17156,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2">
         <v>45403.40102575231</v>
@@ -17138,13 +17177,13 @@
         <v>1410</v>
       </c>
       <c r="H43" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I43" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="J43" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="K43">
         <v>131</v>
@@ -17168,7 +17207,7 @@
         <v>-20.33333333</v>
       </c>
       <c r="V43" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W43">
         <v>0.033333</v>
@@ -17197,10 +17236,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C44" s="2">
         <v>45403.40136972223</v>
@@ -17218,13 +17257,13 @@
         <v>1440</v>
       </c>
       <c r="H44" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I44" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J44" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="K44">
         <v>130</v>
@@ -17248,7 +17287,7 @@
         <v>-20.23333333</v>
       </c>
       <c r="V44" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W44">
         <v>0.003333</v>
@@ -17277,10 +17316,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C45" s="2">
         <v>45403.40171717593</v>
@@ -17298,13 +17337,13 @@
         <v>1470</v>
       </c>
       <c r="H45" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I45" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J45" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K45">
         <v>144</v>
@@ -17328,7 +17367,7 @@
         <v>-19.26666667</v>
       </c>
       <c r="V45" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W45">
         <v>0.032222</v>
@@ -17357,10 +17396,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C46" s="2">
         <v>45403.40206369213</v>
@@ -17378,13 +17417,13 @@
         <v>1500</v>
       </c>
       <c r="H46" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I46" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J46" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="K46">
         <v>150</v>
@@ -17408,7 +17447,7 @@
         <v>-19.66666667</v>
       </c>
       <c r="V46" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W46">
         <v>-0.013333</v>
@@ -17437,10 +17476,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C47" s="2">
         <v>45403.40241096065</v>
@@ -17458,13 +17497,13 @@
         <v>1530</v>
       </c>
       <c r="H47" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I47" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J47" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="K47">
         <v>141</v>
@@ -17488,7 +17527,7 @@
         <v>-19.46666667</v>
       </c>
       <c r="V47" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W47">
         <v>0.006667</v>
@@ -17517,10 +17556,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C48" s="2">
         <v>45403.40275898148</v>
@@ -17538,13 +17577,13 @@
         <v>1560</v>
       </c>
       <c r="H48" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I48" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J48" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K48">
         <v>138</v>
@@ -17568,7 +17607,7 @@
         <v>-20.36666667</v>
       </c>
       <c r="V48" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W48">
         <v>-0.03</v>
@@ -17597,10 +17636,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C49" s="2">
         <v>45403.40310667824</v>
@@ -17618,13 +17657,13 @@
         <v>1590</v>
       </c>
       <c r="H49" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I49" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J49" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="K49">
         <v>139</v>
@@ -17648,7 +17687,7 @@
         <v>-19.66666667</v>
       </c>
       <c r="V49" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W49">
         <v>0.023333</v>
@@ -17677,10 +17716,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C50" s="2">
         <v>45403.40345479167</v>
@@ -17698,13 +17737,13 @@
         <v>1620</v>
       </c>
       <c r="H50" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I50" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J50" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K50">
         <v>135</v>
@@ -17728,7 +17767,7 @@
         <v>-20.36666667</v>
       </c>
       <c r="V50" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W50">
         <v>-0.023333</v>
@@ -17757,10 +17796,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C51" s="2">
         <v>45403.40380133102</v>
@@ -17778,13 +17817,13 @@
         <v>1650</v>
       </c>
       <c r="H51" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I51" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J51" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="K51">
         <v>150</v>
@@ -17808,7 +17847,7 @@
         <v>-20.23333333</v>
       </c>
       <c r="V51" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W51">
         <v>0.004444</v>
@@ -17837,10 +17876,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C52" s="2">
         <v>45403.40414807871</v>
@@ -17858,13 +17897,13 @@
         <v>1680</v>
       </c>
       <c r="H52" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I52" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="J52" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K52">
         <v>143</v>
@@ -17888,7 +17927,7 @@
         <v>-19.8</v>
       </c>
       <c r="V52" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W52">
         <v>0.014444</v>
@@ -17917,10 +17956,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2">
         <v>45403.40449873843</v>
@@ -17938,13 +17977,13 @@
         <v>1710</v>
       </c>
       <c r="H53" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I53" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J53" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="K53">
         <v>147</v>
@@ -17968,7 +18007,7 @@
         <v>-20</v>
       </c>
       <c r="V53" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W53">
         <v>-0.006667</v>
@@ -17997,10 +18036,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C54" s="2">
         <v>45403.40484334491</v>
@@ -18018,13 +18057,13 @@
         <v>1740</v>
       </c>
       <c r="H54" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I54" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J54" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="K54">
         <v>141</v>
@@ -18048,7 +18087,7 @@
         <v>-19.7</v>
       </c>
       <c r="V54" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W54">
         <v>0.01</v>
@@ -18077,10 +18116,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C55" s="2">
         <v>45403.40518871527</v>
@@ -18098,13 +18137,13 @@
         <v>1770</v>
       </c>
       <c r="H55" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I55" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J55" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K55">
         <v>143</v>
@@ -18128,7 +18167,7 @@
         <v>-19.03333333</v>
       </c>
       <c r="V55" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W55">
         <v>0.022222</v>
@@ -18157,10 +18196,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C56" s="2">
         <v>45403.40553603009</v>
@@ -18178,13 +18217,13 @@
         <v>1800</v>
       </c>
       <c r="H56" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I56" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J56" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="K56">
         <v>157</v>
@@ -18208,7 +18247,7 @@
         <v>-18.8</v>
       </c>
       <c r="V56" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W56">
         <v>0.007778</v>
@@ -18237,10 +18276,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2">
         <v>45403.40588310185</v>
@@ -18258,13 +18297,13 @@
         <v>1830</v>
       </c>
       <c r="H57" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I57" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J57" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="K57">
         <v>146</v>
@@ -18288,7 +18327,7 @@
         <v>-18.16666667</v>
       </c>
       <c r="V57" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W57">
         <v>0.021111</v>
@@ -18317,10 +18356,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C58" s="2">
         <v>45403.4065787037</v>
@@ -18338,13 +18377,13 @@
         <v>1890</v>
       </c>
       <c r="H58" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I58" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="J58" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="K58">
         <v>165</v>
@@ -18368,7 +18407,7 @@
         <v>-17.38333333</v>
       </c>
       <c r="V58" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W58">
         <v>0.013056</v>
@@ -18397,10 +18436,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2">
         <v>45403.40692917824</v>
@@ -18418,13 +18457,13 @@
         <v>1920</v>
       </c>
       <c r="H59" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I59" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J59" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="K59">
         <v>151</v>
@@ -18448,7 +18487,7 @@
         <v>-16.83333333</v>
       </c>
       <c r="V59" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W59">
         <v>0.018333</v>
@@ -18477,10 +18516,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C60" s="2">
         <v>45403.40727283565</v>
@@ -18498,13 +18537,13 @@
         <v>1950</v>
       </c>
       <c r="H60" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I60" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J60" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="K60">
         <v>137</v>
@@ -18528,7 +18567,7 @@
         <v>-17.2</v>
       </c>
       <c r="V60" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W60">
         <v>-0.012222</v>
@@ -18557,10 +18596,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C61" s="2">
         <v>45403.40761988426</v>
@@ -18578,13 +18617,13 @@
         <v>1980</v>
       </c>
       <c r="H61" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I61" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="J61" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K61">
         <v>163</v>
@@ -18608,7 +18647,7 @@
         <v>-16.73333333</v>
       </c>
       <c r="V61" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W61">
         <v>0.015556</v>
@@ -18637,10 +18676,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C62" s="2">
         <v>45403.40796920139</v>
@@ -18658,13 +18697,13 @@
         <v>2010</v>
       </c>
       <c r="H62" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I62" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J62" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="K62">
         <v>158</v>
@@ -18688,7 +18727,7 @@
         <v>-17.03333333</v>
       </c>
       <c r="V62" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W62">
         <v>-0.01</v>
@@ -18717,10 +18756,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C63" s="2">
         <v>45403.40831346065</v>
@@ -18738,13 +18777,13 @@
         <v>2040</v>
       </c>
       <c r="H63" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I63" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J63" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="K63">
         <v>150</v>
@@ -18768,7 +18807,7 @@
         <v>-17.06666667</v>
       </c>
       <c r="V63" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W63">
         <v>-0.001111</v>
@@ -18797,10 +18836,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C64" s="2">
         <v>45403.4086615162</v>
@@ -18818,13 +18857,13 @@
         <v>2070</v>
       </c>
       <c r="H64" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I64" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J64" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="K64">
         <v>162</v>
@@ -18848,7 +18887,7 @@
         <v>-17.16666667</v>
       </c>
       <c r="V64" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W64">
         <v>-0.003333</v>
@@ -18877,10 +18916,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C65" s="2">
         <v>45403.4090116088</v>
@@ -18898,13 +18937,13 @@
         <v>2100</v>
       </c>
       <c r="H65" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I65" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="J65" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="K65">
         <v>174</v>
@@ -18928,7 +18967,7 @@
         <v>-17.2</v>
       </c>
       <c r="V65" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W65">
         <v>-0.001111</v>
@@ -18957,10 +18996,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C66" s="2">
         <v>45403.40935710648</v>
@@ -18978,13 +19017,13 @@
         <v>2130</v>
       </c>
       <c r="H66" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I66" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J66" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="K66">
         <v>156</v>
@@ -19008,7 +19047,7 @@
         <v>-16.93333333</v>
       </c>
       <c r="V66" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W66">
         <v>0.008888999999999999</v>
@@ -19037,10 +19076,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C67" s="2">
         <v>45403.40970434028</v>
@@ -19058,13 +19097,13 @@
         <v>2160</v>
       </c>
       <c r="H67" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I67" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J67" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="K67">
         <v>154</v>
@@ -19088,7 +19127,7 @@
         <v>-16.96666667</v>
       </c>
       <c r="V67" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W67">
         <v>-0.001111</v>
@@ -19117,10 +19156,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C68" s="2">
         <v>45403.4100522338</v>
@@ -19138,13 +19177,13 @@
         <v>2190</v>
       </c>
       <c r="H68" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I68" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J68" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="K68">
         <v>139</v>
@@ -19168,7 +19207,7 @@
         <v>-17.4</v>
       </c>
       <c r="V68" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W68">
         <v>-0.014444</v>
@@ -19197,10 +19236,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C69" s="2">
         <v>45403.41040427083</v>
@@ -19218,13 +19257,13 @@
         <v>2220</v>
       </c>
       <c r="H69" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I69" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J69" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="K69">
         <v>163</v>
@@ -19248,7 +19287,7 @@
         <v>-16.5</v>
       </c>
       <c r="V69" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W69">
         <v>0.03</v>
@@ -19277,10 +19316,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C70" s="2">
         <v>45403.4110910301</v>
@@ -19298,13 +19337,13 @@
         <v>2280</v>
       </c>
       <c r="H70" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I70" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="J70" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K70">
         <v>166</v>
@@ -19328,7 +19367,7 @@
         <v>-16.63333333</v>
       </c>
       <c r="V70" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W70">
         <v>-0.002222</v>
@@ -19357,10 +19396,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C71" s="2">
         <v>45403.41143875</v>
@@ -19378,13 +19417,13 @@
         <v>2310</v>
       </c>
       <c r="H71" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I71" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J71" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="K71">
         <v>167</v>
@@ -19408,7 +19447,7 @@
         <v>-16.26666667</v>
       </c>
       <c r="V71" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W71">
         <v>0.012222</v>
@@ -19437,10 +19476,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C72" s="2">
         <v>45403.41178738426</v>
@@ -19458,13 +19497,13 @@
         <v>2340</v>
       </c>
       <c r="H72" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I72" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="J72" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="K72">
         <v>137</v>
@@ -19488,7 +19527,7 @@
         <v>-15.86666667</v>
       </c>
       <c r="V72" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W72">
         <v>0.013333</v>
@@ -19517,10 +19556,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C73" s="2">
         <v>45403.41213525463</v>
@@ -19538,13 +19577,13 @@
         <v>2370</v>
       </c>
       <c r="H73" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I73" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J73" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="K73">
         <v>140</v>
@@ -19568,7 +19607,7 @@
         <v>-16.1</v>
       </c>
       <c r="V73" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W73">
         <v>-0.007778</v>
@@ -19597,10 +19636,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C74" s="2">
         <v>45403.41248388889</v>
@@ -19618,13 +19657,13 @@
         <v>2400</v>
       </c>
       <c r="H74" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I74" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="J74" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="K74">
         <v>157</v>
@@ -19648,7 +19687,7 @@
         <v>-15.3</v>
       </c>
       <c r="V74" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W74">
         <v>0.026667</v>
@@ -19677,10 +19716,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C75" s="2">
         <v>45403.41282869213</v>
@@ -19698,13 +19737,13 @@
         <v>2430</v>
       </c>
       <c r="H75" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I75" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J75" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="K75">
         <v>171</v>
@@ -19728,7 +19767,7 @@
         <v>-15.2</v>
       </c>
       <c r="V75" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W75">
         <v>0.003333</v>
@@ -19757,10 +19796,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C76" s="2">
         <v>45403.41317821759</v>
@@ -19778,13 +19817,13 @@
         <v>2460</v>
       </c>
       <c r="H76" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I76" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="J76" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="K76">
         <v>136</v>
@@ -19808,7 +19847,7 @@
         <v>-15.1</v>
       </c>
       <c r="V76" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W76">
         <v>0.003333</v>
@@ -19837,10 +19876,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C77" s="2">
         <v>45403.41352417824</v>
@@ -19858,13 +19897,13 @@
         <v>2490</v>
       </c>
       <c r="H77" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I77" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J77" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="K77">
         <v>123</v>
@@ -19888,7 +19927,7 @@
         <v>-15.63333333</v>
       </c>
       <c r="V77" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W77">
         <v>-0.017778</v>
@@ -19917,10 +19956,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C78" s="2">
         <v>45403.41387609953</v>
@@ -19938,13 +19977,13 @@
         <v>2520</v>
       </c>
       <c r="H78" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I78" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="J78" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="K78">
         <v>160</v>
@@ -19968,7 +20007,7 @@
         <v>-14.43333333</v>
       </c>
       <c r="V78" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W78">
         <v>0.04</v>
@@ -19997,10 +20036,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C79" s="2">
         <v>45403.41421701389</v>
@@ -20018,13 +20057,13 @@
         <v>2550</v>
       </c>
       <c r="H79" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I79" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="J79" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="K79">
         <v>122</v>
@@ -20048,7 +20087,7 @@
         <v>-14.56666667</v>
       </c>
       <c r="V79" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W79">
         <v>-0.004444</v>
@@ -20077,10 +20116,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C80" s="2">
         <v>45403.41456357639</v>
@@ -20098,13 +20137,13 @@
         <v>2580</v>
       </c>
       <c r="H80" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I80" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="J80" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="K80">
         <v>103</v>
@@ -20128,7 +20167,7 @@
         <v>-14.3</v>
       </c>
       <c r="V80" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W80">
         <v>0.008888999999999999</v>
@@ -20157,10 +20196,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C81" s="2">
         <v>45403.41491677083</v>
@@ -20178,13 +20217,13 @@
         <v>2610</v>
       </c>
       <c r="H81" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I81" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J81" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="K81">
         <v>90</v>
@@ -20208,7 +20247,7 @@
         <v>-15.43333333</v>
       </c>
       <c r="V81" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W81">
         <v>-0.037778</v>
@@ -20237,10 +20276,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C82" s="2">
         <v>45403.41560888889</v>
@@ -20258,13 +20297,13 @@
         <v>2670</v>
       </c>
       <c r="H82" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I82" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J82" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="K82">
         <v>68</v>
@@ -20288,7 +20327,7 @@
         <v>-15.15</v>
       </c>
       <c r="V82" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W82">
         <v>0.004722</v>
@@ -20317,10 +20356,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C83" s="2">
         <v>45403.41595309028</v>
@@ -20338,13 +20377,13 @@
         <v>2700</v>
       </c>
       <c r="H83" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I83" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="J83" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K83">
         <v>148</v>
@@ -20368,7 +20407,7 @@
         <v>-14.86666667</v>
       </c>
       <c r="V83" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W83">
         <v>0.009443999999999999</v>
@@ -20397,10 +20436,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C84" s="2">
         <v>45403.41630097223</v>
@@ -20418,13 +20457,13 @@
         <v>2730</v>
       </c>
       <c r="H84" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I84" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="J84" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="K84">
         <v>93</v>
@@ -20448,7 +20487,7 @@
         <v>-14.66666667</v>
       </c>
       <c r="V84" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W84">
         <v>0.006667</v>
@@ -20477,10 +20516,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C85" s="2">
         <v>45403.41664903935</v>
@@ -20498,13 +20537,13 @@
         <v>2760</v>
       </c>
       <c r="H85" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I85" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="J85" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K85">
         <v>349</v>
@@ -20528,7 +20567,7 @@
         <v>-15.1</v>
       </c>
       <c r="V85" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W85">
         <v>-0.014444</v>
@@ -20557,10 +20596,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C86" s="2">
         <v>45403.41734554398</v>
@@ -20578,13 +20617,13 @@
         <v>2820</v>
       </c>
       <c r="H86" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I86" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="J86" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="K86">
         <v>13</v>
@@ -20608,7 +20647,7 @@
         <v>-14</v>
       </c>
       <c r="V86" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W86">
         <v>0.018333</v>

--- a/www/flightdata/xlsx/eoss-357.xlsx
+++ b/www/flightdata/xlsx/eoss-357.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="527">
   <si>
     <t>flight</t>
   </si>
@@ -228,6 +228,9 @@
     <t>velocity_curvefit</t>
   </si>
   <si>
+    <t>reynolds_transition</t>
+  </si>
+  <si>
     <t>KC0D-3</t>
   </si>
   <si>
@@ -1075,6 +1078,9 @@
   </si>
   <si>
     <t>low Re</t>
+  </si>
+  <si>
+    <t>high_to_low</t>
   </si>
   <si>
     <t>descending</t>
@@ -2116,10 +2122,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE140"/>
+  <dimension ref="A1:AF140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -2213,13 +2219,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>45403.3397934838</v>
@@ -2237,13 +2246,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K2">
         <v>23</v>
@@ -2282,7 +2291,7 @@
         <v>6.6</v>
       </c>
       <c r="W2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y2">
         <v>6.6</v>
@@ -2291,12 +2300,12 @@
         <v>12.326114</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>45403.33991818287</v>
@@ -2314,13 +2323,13 @@
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K3">
         <v>300</v>
@@ -2347,7 +2356,7 @@
         <v>17.7</v>
       </c>
       <c r="W3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X3">
         <v>0.37</v>
@@ -2368,12 +2377,12 @@
         <v>15.026715</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>45403.34010142361</v>
@@ -2391,13 +2400,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K4">
         <v>29</v>
@@ -2436,7 +2445,7 @@
         <v>22.56666667</v>
       </c>
       <c r="W4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X4">
         <v>0.162222</v>
@@ -2463,12 +2472,12 @@
         <v>17.113537</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>45403.34025924769</v>
@@ -2486,13 +2495,13 @@
         <v>47</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K5">
         <v>337</v>
@@ -2519,7 +2528,7 @@
         <v>19.26666667</v>
       </c>
       <c r="W5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X5">
         <v>-0.11</v>
@@ -2546,12 +2555,12 @@
         <v>18.361213</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>45403.34048710648</v>
@@ -2569,13 +2578,13 @@
         <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K6">
         <v>354</v>
@@ -2614,7 +2623,7 @@
         <v>19.86666667</v>
       </c>
       <c r="W6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X6">
         <v>0.02</v>
@@ -2641,12 +2650,12 @@
         <v>19.782631</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>45403.34060564815</v>
@@ -2664,13 +2673,13 @@
         <v>77</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K7">
         <v>55</v>
@@ -2697,7 +2706,7 @@
         <v>21.86666667</v>
       </c>
       <c r="W7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X7">
         <v>0.066667</v>
@@ -2724,12 +2733,12 @@
         <v>20.717148</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>45403.3408002662</v>
@@ -2747,13 +2756,13 @@
         <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K8">
         <v>124</v>
@@ -2792,7 +2801,7 @@
         <v>22</v>
       </c>
       <c r="W8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X8">
         <v>0.004444</v>
@@ -2819,12 +2828,12 @@
         <v>21.511402</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2">
         <v>45403.34095277778</v>
@@ -2842,13 +2851,13 @@
         <v>107</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K9">
         <v>12</v>
@@ -2875,7 +2884,7 @@
         <v>19.7</v>
       </c>
       <c r="W9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X9">
         <v>-0.076667</v>
@@ -2902,12 +2911,12 @@
         <v>21.89242</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2">
         <v>45403.34118518519</v>
@@ -2925,13 +2934,13 @@
         <v>120</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K10">
         <v>193</v>
@@ -2970,7 +2979,7 @@
         <v>20.03333333</v>
       </c>
       <c r="W10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X10">
         <v>0.011111</v>
@@ -2997,12 +3006,12 @@
         <v>22.291936</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2">
         <v>45403.34130043982</v>
@@ -3020,13 +3029,13 @@
         <v>137</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K11">
         <v>37</v>
@@ -3053,7 +3062,7 @@
         <v>21.2</v>
       </c>
       <c r="W11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X11">
         <v>0.038889</v>
@@ -3080,12 +3089,12 @@
         <v>22.465832</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2">
         <v>45403.34148907408</v>
@@ -3103,13 +3112,13 @@
         <v>150</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K12">
         <v>110</v>
@@ -3148,7 +3157,7 @@
         <v>21.26666667</v>
       </c>
       <c r="W12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X12">
         <v>0.002222</v>
@@ -3175,12 +3184,12 @@
         <v>22.570959</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2">
         <v>45403.34164728009</v>
@@ -3198,13 +3207,13 @@
         <v>167</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K13">
         <v>163</v>
@@ -3231,7 +3240,7 @@
         <v>22.43333333</v>
       </c>
       <c r="W13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X13">
         <v>0.038889</v>
@@ -3258,12 +3267,12 @@
         <v>22.570113</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2">
         <v>45403.34186986111</v>
@@ -3281,13 +3290,13 @@
         <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K14">
         <v>164</v>
@@ -3326,7 +3335,7 @@
         <v>23.06666667</v>
       </c>
       <c r="W14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X14">
         <v>0.021111</v>
@@ -3353,12 +3362,12 @@
         <v>22.486993</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2">
         <v>45403.34199619213</v>
@@ -3376,13 +3385,13 @@
         <v>197</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K15">
         <v>177</v>
@@ -3409,7 +3418,7 @@
         <v>21.96666667</v>
       </c>
       <c r="W15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X15">
         <v>-0.036667</v>
@@ -3436,12 +3445,12 @@
         <v>22.390024</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2">
         <v>45403.34218773148</v>
@@ -3459,13 +3468,13 @@
         <v>210</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K16">
         <v>172</v>
@@ -3504,7 +3513,7 @@
         <v>21.93333333</v>
       </c>
       <c r="W16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X16">
         <v>-0.001111</v>
@@ -3536,7 +3545,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2">
         <v>45403.34234268519</v>
@@ -3554,13 +3563,13 @@
         <v>227</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K17">
         <v>197</v>
@@ -3587,7 +3596,7 @@
         <v>22.86666667</v>
       </c>
       <c r="W17" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X17">
         <v>0.031111</v>
@@ -3619,7 +3628,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2">
         <v>45403.34257021991</v>
@@ -3637,13 +3646,13 @@
         <v>240</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K18">
         <v>147</v>
@@ -3682,7 +3691,7 @@
         <v>22.1</v>
       </c>
       <c r="W18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X18">
         <v>-0.025556</v>
@@ -3714,7 +3723,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2">
         <v>45403.34268951389</v>
@@ -3732,13 +3741,13 @@
         <v>257</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K19">
         <v>136</v>
@@ -3765,7 +3774,7 @@
         <v>22</v>
       </c>
       <c r="W19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X19">
         <v>-0.003333</v>
@@ -3797,7 +3806,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2">
         <v>45403.34288285879</v>
@@ -3815,13 +3824,13 @@
         <v>270</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K20">
         <v>149</v>
@@ -3860,7 +3869,7 @@
         <v>21.93333333</v>
       </c>
       <c r="W20" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X20">
         <v>-0.002222</v>
@@ -3892,7 +3901,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2">
         <v>45403.34303712963</v>
@@ -3910,13 +3919,13 @@
         <v>287</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K21">
         <v>110</v>
@@ -3943,7 +3952,7 @@
         <v>21.2</v>
       </c>
       <c r="W21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X21">
         <v>-0.024444</v>
@@ -3975,7 +3984,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2">
         <v>45403.34326444445</v>
@@ -3993,13 +4002,13 @@
         <v>300</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K22">
         <v>157</v>
@@ -4038,7 +4047,7 @@
         <v>21.63333333</v>
       </c>
       <c r="W22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X22">
         <v>0.014444</v>
@@ -4070,7 +4079,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2">
         <v>45403.34338399306</v>
@@ -4088,13 +4097,13 @@
         <v>317</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K23">
         <v>161</v>
@@ -4121,7 +4130,7 @@
         <v>20.8</v>
       </c>
       <c r="W23" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X23">
         <v>-0.027778</v>
@@ -4153,7 +4162,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>45403.34357177083</v>
@@ -4171,13 +4180,13 @@
         <v>330</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K24">
         <v>156</v>
@@ -4216,7 +4225,7 @@
         <v>21.56666667</v>
       </c>
       <c r="W24" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X24">
         <v>0.025556</v>
@@ -4248,7 +4257,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2">
         <v>45403.34395445602</v>
@@ -4266,13 +4275,13 @@
         <v>360</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K25">
         <v>125</v>
@@ -4311,7 +4320,7 @@
         <v>22.76666667</v>
       </c>
       <c r="W25" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X25">
         <v>0.04</v>
@@ -4343,7 +4352,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="2">
         <v>45403.34427366898</v>
@@ -4361,13 +4370,13 @@
         <v>390</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K26">
         <v>143</v>
@@ -4406,7 +4415,7 @@
         <v>21.36666667</v>
       </c>
       <c r="W26" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X26">
         <v>-0.046667</v>
@@ -4438,7 +4447,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="2">
         <v>45403.34442540509</v>
@@ -4456,13 +4465,13 @@
         <v>407</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K27">
         <v>153</v>
@@ -4489,7 +4498,7 @@
         <v>22.42222222</v>
       </c>
       <c r="W27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X27">
         <v>0.011728</v>
@@ -4521,7 +4530,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2">
         <v>45403.34464880787</v>
@@ -4539,13 +4548,13 @@
         <v>420</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K28">
         <v>145</v>
@@ -4584,7 +4593,7 @@
         <v>22.36666667</v>
       </c>
       <c r="W28" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X28">
         <v>-0.001852</v>
@@ -4616,7 +4625,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2">
         <v>45403.34477232639</v>
@@ -4634,13 +4643,13 @@
         <v>437</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K29">
         <v>150</v>
@@ -4667,7 +4676,7 @@
         <v>21.76666667</v>
       </c>
       <c r="W29" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X29">
         <v>-0.02</v>
@@ -4699,7 +4708,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>45403.34511964121</v>
@@ -4717,13 +4726,13 @@
         <v>467</v>
       </c>
       <c r="H30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K30">
         <v>163</v>
@@ -4750,7 +4759,7 @@
         <v>21.43333333</v>
       </c>
       <c r="W30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X30">
         <v>-0.011111</v>
@@ -4782,7 +4791,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2">
         <v>45403.34534288194</v>
@@ -4800,13 +4809,13 @@
         <v>480</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K31">
         <v>158</v>
@@ -4845,7 +4854,7 @@
         <v>21.58333333</v>
       </c>
       <c r="W31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X31">
         <v>0.0025</v>
@@ -4877,7 +4886,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>45403.34546665509</v>
@@ -4895,13 +4904,13 @@
         <v>497</v>
       </c>
       <c r="H32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K32">
         <v>172</v>
@@ -4928,7 +4937,7 @@
         <v>21.96666667</v>
       </c>
       <c r="W32" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X32">
         <v>0.012778</v>
@@ -4960,7 +4969,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2">
         <v>45403.34581424769</v>
@@ -4978,13 +4987,13 @@
         <v>527</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J33" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K33">
         <v>157</v>
@@ -5011,7 +5020,7 @@
         <v>24.16666667</v>
       </c>
       <c r="W33" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X33">
         <v>0.073333</v>
@@ -5043,7 +5052,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2">
         <v>45403.3460388426</v>
@@ -5061,13 +5070,13 @@
         <v>540</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K34">
         <v>157</v>
@@ -5106,7 +5115,7 @@
         <v>23.33333333</v>
       </c>
       <c r="W34" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X34">
         <v>-0.013889</v>
@@ -5138,7 +5147,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>45403.34616277778</v>
@@ -5156,13 +5165,13 @@
         <v>557</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K35">
         <v>129</v>
@@ -5189,7 +5198,7 @@
         <v>22.76666667</v>
       </c>
       <c r="W35" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X35">
         <v>-0.018889</v>
@@ -5221,7 +5230,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>45403.34635535879</v>
@@ -5239,13 +5248,13 @@
         <v>570</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K36">
         <v>145</v>
@@ -5284,7 +5293,7 @@
         <v>22.53333333</v>
       </c>
       <c r="W36" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X36">
         <v>-0.007778</v>
@@ -5316,7 +5325,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2">
         <v>45403.34651185185</v>
@@ -5334,13 +5343,13 @@
         <v>587</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K37">
         <v>163</v>
@@ -5367,7 +5376,7 @@
         <v>22.73333333</v>
       </c>
       <c r="W37" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X37">
         <v>0.006667</v>
@@ -5399,7 +5408,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>45403.34685717593</v>
@@ -5417,13 +5426,13 @@
         <v>617</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K38">
         <v>152</v>
@@ -5450,7 +5459,7 @@
         <v>24.06666667</v>
       </c>
       <c r="W38" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X38">
         <v>0.044444</v>
@@ -5482,7 +5491,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2">
         <v>45403.34720423611</v>
@@ -5500,13 +5509,13 @@
         <v>647</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K39">
         <v>152</v>
@@ -5533,7 +5542,7 @@
         <v>22.53333333</v>
       </c>
       <c r="W39" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X39">
         <v>-0.051111</v>
@@ -5565,7 +5574,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>45403.34755070602</v>
@@ -5583,13 +5592,13 @@
         <v>677</v>
       </c>
       <c r="H40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K40">
         <v>137</v>
@@ -5616,7 +5625,7 @@
         <v>22.96666667</v>
       </c>
       <c r="W40" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X40">
         <v>0.014444</v>
@@ -5648,7 +5657,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2">
         <v>45403.34789796297</v>
@@ -5666,13 +5675,13 @@
         <v>707</v>
       </c>
       <c r="H41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K41">
         <v>157</v>
@@ -5699,7 +5708,7 @@
         <v>23.2</v>
       </c>
       <c r="W41" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X41">
         <v>0.007778</v>
@@ -5731,7 +5740,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>45403.34824575231</v>
@@ -5749,13 +5758,13 @@
         <v>737</v>
       </c>
       <c r="H42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K42">
         <v>139</v>
@@ -5782,7 +5791,7 @@
         <v>23.4</v>
       </c>
       <c r="W42" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X42">
         <v>0.006667</v>
@@ -5814,7 +5823,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2">
         <v>45403.34843268518</v>
@@ -5832,13 +5841,13 @@
         <v>750</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J43" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K43">
         <v>150</v>
@@ -5877,7 +5886,7 @@
         <v>23.06666667</v>
       </c>
       <c r="W43" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X43">
         <v>-0.001852</v>
@@ -5909,7 +5918,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2">
         <v>45403.34859243056</v>
@@ -5927,13 +5936,13 @@
         <v>767</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J44" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K44">
         <v>136</v>
@@ -5960,7 +5969,7 @@
         <v>22.76666667</v>
       </c>
       <c r="W44" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X44">
         <v>-0.01</v>
@@ -5992,7 +6001,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" s="2">
         <v>45403.34893930556</v>
@@ -6010,13 +6019,13 @@
         <v>797</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J45" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K45">
         <v>140</v>
@@ -6043,7 +6052,7 @@
         <v>24.26666667</v>
       </c>
       <c r="W45" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X45">
         <v>0.05</v>
@@ -6075,7 +6084,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2">
         <v>45403.34929054398</v>
@@ -6093,13 +6102,13 @@
         <v>827</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J46" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K46">
         <v>147</v>
@@ -6126,7 +6135,7 @@
         <v>24.83333333</v>
       </c>
       <c r="W46" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X46">
         <v>0.018889</v>
@@ -6158,7 +6167,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="2">
         <v>45403.3495095949</v>
@@ -6176,13 +6185,13 @@
         <v>840</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K47">
         <v>150</v>
@@ -6221,7 +6230,7 @@
         <v>24.01111111</v>
       </c>
       <c r="W47" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X47">
         <v>-0.009136</v>
@@ -6253,7 +6262,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="2">
         <v>45403.34963349537</v>
@@ -6271,13 +6280,13 @@
         <v>857</v>
       </c>
       <c r="H48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K48">
         <v>136</v>
@@ -6304,7 +6313,7 @@
         <v>22.1</v>
       </c>
       <c r="W48" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X48">
         <v>-0.063704</v>
@@ -6336,7 +6345,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>45403.3499822338</v>
@@ -6354,13 +6363,13 @@
         <v>887</v>
       </c>
       <c r="H49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K49">
         <v>145</v>
@@ -6387,7 +6396,7 @@
         <v>23.6</v>
       </c>
       <c r="W49" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X49">
         <v>0.05</v>
@@ -6419,7 +6428,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2">
         <v>45403.35020350695</v>
@@ -6437,13 +6446,13 @@
         <v>900</v>
       </c>
       <c r="H50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K50">
         <v>138</v>
@@ -6482,7 +6491,7 @@
         <v>22.55</v>
       </c>
       <c r="W50" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X50">
         <v>-0.0175</v>
@@ -6514,7 +6523,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>45403.35032831018</v>
@@ -6532,13 +6541,13 @@
         <v>917</v>
       </c>
       <c r="H51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K51">
         <v>130</v>
@@ -6565,7 +6574,7 @@
         <v>21.76666667</v>
       </c>
       <c r="W51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X51">
         <v>-0.026111</v>
@@ -6597,7 +6606,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>45403.3505168287</v>
@@ -6615,13 +6624,13 @@
         <v>930</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K52">
         <v>149</v>
@@ -6660,7 +6669,7 @@
         <v>22.16666667</v>
       </c>
       <c r="W52" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X52">
         <v>0.013333</v>
@@ -6692,7 +6701,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>45403.35067704861</v>
@@ -6710,13 +6719,13 @@
         <v>947</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J53" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K53">
         <v>153</v>
@@ -6743,7 +6752,7 @@
         <v>21.43333333</v>
       </c>
       <c r="W53" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X53">
         <v>-0.024444</v>
@@ -6775,7 +6784,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>45403.35089872685</v>
@@ -6793,13 +6802,13 @@
         <v>960</v>
       </c>
       <c r="H54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J54" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K54">
         <v>141</v>
@@ -6838,7 +6847,7 @@
         <v>20.83333333</v>
       </c>
       <c r="W54" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X54">
         <v>-0.02</v>
@@ -6870,7 +6879,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>45403.35102598379</v>
@@ -6888,13 +6897,13 @@
         <v>977</v>
       </c>
       <c r="H55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J55" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K55">
         <v>131</v>
@@ -6921,7 +6930,7 @@
         <v>20.9</v>
       </c>
       <c r="W55" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X55">
         <v>0.002222</v>
@@ -6953,7 +6962,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C56" s="2">
         <v>45403.351369375</v>
@@ -6971,13 +6980,13 @@
         <v>1007</v>
       </c>
       <c r="H56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J56" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K56">
         <v>130</v>
@@ -7004,7 +7013,7 @@
         <v>24.73333333</v>
       </c>
       <c r="W56" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X56">
         <v>0.127778</v>
@@ -7036,7 +7045,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C57" s="2">
         <v>45403.35159295139</v>
@@ -7054,13 +7063,13 @@
         <v>1020</v>
       </c>
       <c r="H57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K57">
         <v>146</v>
@@ -7099,7 +7108,7 @@
         <v>23.51666667</v>
       </c>
       <c r="W57" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X57">
         <v>-0.020278</v>
@@ -7131,7 +7140,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="2">
         <v>45403.35172105324</v>
@@ -7149,13 +7158,13 @@
         <v>1037</v>
       </c>
       <c r="H58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K58">
         <v>148</v>
@@ -7182,7 +7191,7 @@
         <v>22.86666667</v>
       </c>
       <c r="W58" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X58">
         <v>-0.021667</v>
@@ -7214,7 +7223,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2">
         <v>45403.35206660879</v>
@@ -7232,13 +7241,13 @@
         <v>1067</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K59">
         <v>129</v>
@@ -7265,7 +7274,7 @@
         <v>22.73333333</v>
       </c>
       <c r="W59" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X59">
         <v>-0.004444</v>
@@ -7297,7 +7306,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2">
         <v>45403.35228770833</v>
@@ -7315,13 +7324,13 @@
         <v>1080</v>
       </c>
       <c r="H60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J60" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K60">
         <v>129</v>
@@ -7360,7 +7369,7 @@
         <v>23.1</v>
       </c>
       <c r="W60" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X60">
         <v>0.006111</v>
@@ -7392,7 +7401,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="2">
         <v>45403.35241101852</v>
@@ -7410,13 +7419,13 @@
         <v>1097</v>
       </c>
       <c r="H61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J61" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K61">
         <v>125</v>
@@ -7443,7 +7452,7 @@
         <v>24.16666667</v>
       </c>
       <c r="W61" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X61">
         <v>0.035556</v>
@@ -7475,7 +7484,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2">
         <v>45403.35275898148</v>
@@ -7493,13 +7502,13 @@
         <v>1127</v>
       </c>
       <c r="H62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K62">
         <v>132</v>
@@ -7526,7 +7535,7 @@
         <v>23.53333333</v>
       </c>
       <c r="W62" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X62">
         <v>-0.021111</v>
@@ -7558,7 +7567,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2">
         <v>45403.35298197917</v>
@@ -7576,13 +7585,13 @@
         <v>1140</v>
       </c>
       <c r="H63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J63" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K63">
         <v>138</v>
@@ -7621,7 +7630,7 @@
         <v>23.7</v>
       </c>
       <c r="W63" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X63">
         <v>0.002778</v>
@@ -7653,7 +7662,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2">
         <v>45403.353105625</v>
@@ -7671,13 +7680,13 @@
         <v>1157</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K64">
         <v>126</v>
@@ -7704,7 +7713,7 @@
         <v>25.56666667</v>
       </c>
       <c r="W64" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X64">
         <v>0.062222</v>
@@ -7736,7 +7745,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C65" s="2">
         <v>45403.35329466435</v>
@@ -7754,13 +7763,13 @@
         <v>1170</v>
       </c>
       <c r="H65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J65" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K65">
         <v>135</v>
@@ -7799,7 +7808,7 @@
         <v>25.96666667</v>
       </c>
       <c r="W65" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X65">
         <v>0.013333</v>
@@ -7831,7 +7840,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2">
         <v>45403.35345396991</v>
@@ -7849,13 +7858,13 @@
         <v>1187</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J66" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K66">
         <v>131</v>
@@ -7882,7 +7891,7 @@
         <v>25.26666667</v>
       </c>
       <c r="W66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X66">
         <v>-0.023333</v>
@@ -7914,7 +7923,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2">
         <v>45403.35367688657</v>
@@ -7932,13 +7941,13 @@
         <v>1200</v>
       </c>
       <c r="H67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J67" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K67">
         <v>131</v>
@@ -7977,7 +7986,7 @@
         <v>25.56666667</v>
       </c>
       <c r="W67" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X67">
         <v>0.01</v>
@@ -8009,7 +8018,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2">
         <v>45403.35380072916</v>
@@ -8027,13 +8036,13 @@
         <v>1217</v>
       </c>
       <c r="H68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K68">
         <v>133</v>
@@ -8060,7 +8069,7 @@
         <v>25.83333333</v>
       </c>
       <c r="W68" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X68">
         <v>0.008888999999999999</v>
@@ -8092,7 +8101,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2">
         <v>45403.35414768518</v>
@@ -8110,13 +8119,13 @@
         <v>1247</v>
       </c>
       <c r="H69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K69">
         <v>144</v>
@@ -8143,7 +8152,7 @@
         <v>27.13333333</v>
       </c>
       <c r="W69" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X69">
         <v>0.043333</v>
@@ -8175,7 +8184,7 @@
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C70" s="2">
         <v>45403.35437109954</v>
@@ -8193,13 +8202,13 @@
         <v>1260</v>
       </c>
       <c r="H70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K70">
         <v>132</v>
@@ -8238,7 +8247,7 @@
         <v>26.51666667</v>
       </c>
       <c r="W70" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X70">
         <v>-0.010278</v>
@@ -8270,7 +8279,7 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2">
         <v>45403.35449524305</v>
@@ -8288,13 +8297,13 @@
         <v>1277</v>
       </c>
       <c r="H71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J71" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K71">
         <v>127</v>
@@ -8321,7 +8330,7 @@
         <v>27.23333333</v>
       </c>
       <c r="W71" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X71">
         <v>0.023889</v>
@@ -8353,7 +8362,7 @@
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2">
         <v>45403.35484331018</v>
@@ -8371,13 +8380,13 @@
         <v>1307</v>
       </c>
       <c r="H72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J72" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K72">
         <v>149</v>
@@ -8404,7 +8413,7 @@
         <v>29.63333333</v>
       </c>
       <c r="W72" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X72">
         <v>0.08</v>
@@ -8436,7 +8445,7 @@
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C73" s="2">
         <v>45403.35506581019</v>
@@ -8454,13 +8463,13 @@
         <v>1320</v>
       </c>
       <c r="H73" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J73" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K73">
         <v>144</v>
@@ -8499,7 +8508,7 @@
         <v>27.81666667</v>
       </c>
       <c r="W73" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X73">
         <v>-0.030278</v>
@@ -8531,7 +8540,7 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="2">
         <v>45403.3551937963</v>
@@ -8549,13 +8558,13 @@
         <v>1337</v>
       </c>
       <c r="H74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J74" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K74">
         <v>146</v>
@@ -8582,7 +8591,7 @@
         <v>22.63333333</v>
       </c>
       <c r="W74" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X74">
         <v>-0.172778</v>
@@ -8614,7 +8623,7 @@
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C75" s="2">
         <v>45403.35537799769</v>
@@ -8632,13 +8641,13 @@
         <v>1350</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J75" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K75">
         <v>138</v>
@@ -8677,7 +8686,7 @@
         <v>23.23333333</v>
       </c>
       <c r="W75" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X75">
         <v>0.02</v>
@@ -8709,7 +8718,7 @@
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="2">
         <v>45403.35554219907</v>
@@ -8727,13 +8736,13 @@
         <v>1367</v>
       </c>
       <c r="H76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J76" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K76">
         <v>145</v>
@@ -8760,7 +8769,7 @@
         <v>24.83333333</v>
       </c>
       <c r="W76" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X76">
         <v>0.053333</v>
@@ -8792,7 +8801,7 @@
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C77" s="2">
         <v>45403.35576005787</v>
@@ -8810,13 +8819,13 @@
         <v>1380</v>
       </c>
       <c r="H77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J77" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K77">
         <v>131</v>
@@ -8855,7 +8864,7 @@
         <v>25.86666667</v>
       </c>
       <c r="W77" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X77">
         <v>0.034444</v>
@@ -8887,7 +8896,7 @@
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C78" s="2">
         <v>45403.35588299768</v>
@@ -8905,13 +8914,13 @@
         <v>1397</v>
       </c>
       <c r="H78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J78" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K78">
         <v>136</v>
@@ -8938,7 +8947,7 @@
         <v>25.46666667</v>
       </c>
       <c r="W78" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X78">
         <v>-0.013333</v>
@@ -8970,7 +8979,7 @@
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C79" s="2">
         <v>45403.35607357639</v>
@@ -8988,13 +8997,13 @@
         <v>1410</v>
       </c>
       <c r="H79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J79" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K79">
         <v>128</v>
@@ -9033,7 +9042,7 @@
         <v>27.06666667</v>
       </c>
       <c r="W79" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X79">
         <v>0.053333</v>
@@ -9065,7 +9074,7 @@
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="2">
         <v>45403.35623045139</v>
@@ -9083,13 +9092,13 @@
         <v>1427</v>
       </c>
       <c r="H80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J80" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K80">
         <v>132</v>
@@ -9116,7 +9125,7 @@
         <v>26.6</v>
       </c>
       <c r="W80" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X80">
         <v>-0.015556</v>
@@ -9148,7 +9157,7 @@
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="2">
         <v>45403.35657739583</v>
@@ -9166,13 +9175,13 @@
         <v>1457</v>
       </c>
       <c r="H81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J81" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K81">
         <v>110</v>
@@ -9199,7 +9208,7 @@
         <v>24.7</v>
       </c>
       <c r="W81" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X81">
         <v>-0.063333</v>
@@ -9231,7 +9240,7 @@
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C82" s="2">
         <v>45403.35676763889</v>
@@ -9249,13 +9258,13 @@
         <v>1470</v>
       </c>
       <c r="H82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J82" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K82">
         <v>126</v>
@@ -9294,7 +9303,7 @@
         <v>25.78333333</v>
       </c>
       <c r="W82" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X82">
         <v>0.018056</v>
@@ -9326,7 +9335,7 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C83" s="2">
         <v>45403.35692618055</v>
@@ -9344,13 +9353,13 @@
         <v>1487</v>
       </c>
       <c r="H83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J83" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K83">
         <v>123</v>
@@ -9377,7 +9386,7 @@
         <v>29.53333333</v>
       </c>
       <c r="W83" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X83">
         <v>0.125</v>
@@ -9409,7 +9418,7 @@
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C84" s="2">
         <v>45403.3571484838</v>
@@ -9427,13 +9436,13 @@
         <v>1500</v>
       </c>
       <c r="H84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J84" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K84">
         <v>125</v>
@@ -9472,7 +9481,7 @@
         <v>28.3</v>
       </c>
       <c r="W84" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X84">
         <v>-0.041111</v>
@@ -9504,7 +9513,7 @@
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="2">
         <v>45403.35727391204</v>
@@ -9522,13 +9531,13 @@
         <v>1517</v>
       </c>
       <c r="H85" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J85" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K85">
         <v>122</v>
@@ -9555,7 +9564,7 @@
         <v>28.76666667</v>
       </c>
       <c r="W85" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X85">
         <v>0.015556</v>
@@ -9587,7 +9596,7 @@
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C86" s="2">
         <v>45403.35746136574</v>
@@ -9605,13 +9614,13 @@
         <v>1530</v>
       </c>
       <c r="H86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J86" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K86">
         <v>135</v>
@@ -9650,7 +9659,7 @@
         <v>28.76666667</v>
       </c>
       <c r="W86" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X86">
         <v>0</v>
@@ -9682,7 +9691,7 @@
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2">
         <v>45403.35762188657</v>
@@ -9700,13 +9709,13 @@
         <v>1547</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J87" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K87">
         <v>142</v>
@@ -9733,7 +9742,7 @@
         <v>26.8</v>
       </c>
       <c r="W87" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X87">
         <v>-0.065556</v>
@@ -9765,7 +9774,7 @@
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C88" s="2">
         <v>45403.35796847222</v>
@@ -9783,13 +9792,13 @@
         <v>1577</v>
       </c>
       <c r="H88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J88" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K88">
         <v>101</v>
@@ -9816,7 +9825,7 @@
         <v>23.3</v>
       </c>
       <c r="W88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X88">
         <v>-0.116667</v>
@@ -9848,7 +9857,7 @@
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="2">
         <v>45403.35831515046</v>
@@ -9866,13 +9875,13 @@
         <v>1607</v>
       </c>
       <c r="H89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J89" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K89">
         <v>120</v>
@@ -9899,7 +9908,7 @@
         <v>27.23333333</v>
       </c>
       <c r="W89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X89">
         <v>0.131111</v>
@@ -9931,7 +9940,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2">
         <v>45403.35853854167</v>
@@ -9949,13 +9958,13 @@
         <v>1620</v>
       </c>
       <c r="H90" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J90" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K90">
         <v>113</v>
@@ -9994,7 +10003,7 @@
         <v>25.22222222</v>
       </c>
       <c r="W90" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X90">
         <v>-0.022346</v>
@@ -10026,7 +10035,7 @@
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2">
         <v>45403.35866368056</v>
@@ -10044,13 +10053,13 @@
         <v>1637</v>
       </c>
       <c r="H91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J91" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K91">
         <v>105</v>
@@ -10077,7 +10086,7 @@
         <v>23.63333333</v>
       </c>
       <c r="W91" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X91">
         <v>-0.052963</v>
@@ -10109,7 +10118,7 @@
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C92" s="2">
         <v>45403.35935561343</v>
@@ -10127,13 +10136,13 @@
         <v>1697</v>
       </c>
       <c r="H92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I92" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J92" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K92">
         <v>122</v>
@@ -10160,7 +10169,7 @@
         <v>22.96666667</v>
       </c>
       <c r="W92" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X92">
         <v>-0.011111</v>
@@ -10192,7 +10201,7 @@
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93" s="2">
         <v>45403.35970369213</v>
@@ -10210,13 +10219,13 @@
         <v>1727</v>
       </c>
       <c r="H93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J93" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K93">
         <v>103</v>
@@ -10243,7 +10252,7 @@
         <v>24.6</v>
       </c>
       <c r="W93" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X93">
         <v>0.054444</v>
@@ -10275,7 +10284,7 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2">
         <v>45403.35992748843</v>
@@ -10293,13 +10302,13 @@
         <v>1740</v>
       </c>
       <c r="H94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K94">
         <v>118</v>
@@ -10338,7 +10347,7 @@
         <v>23.11666667</v>
       </c>
       <c r="W94" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X94">
         <v>-0.012361</v>
@@ -10370,7 +10379,7 @@
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C95" s="2">
         <v>45403.3600502199</v>
@@ -10388,13 +10397,13 @@
         <v>1757</v>
       </c>
       <c r="H95" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K95">
         <v>96</v>
@@ -10421,7 +10430,7 @@
         <v>20.8</v>
       </c>
       <c r="W95" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X95">
         <v>-0.077222</v>
@@ -10453,7 +10462,7 @@
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C96" s="2">
         <v>45403.36039835648</v>
@@ -10471,13 +10480,13 @@
         <v>1787</v>
       </c>
       <c r="H96" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J96" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K96">
         <v>101</v>
@@ -10504,7 +10513,7 @@
         <v>24.7</v>
       </c>
       <c r="W96" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X96">
         <v>0.13</v>
@@ -10531,12 +10540,12 @@
         <v>22.137518</v>
       </c>
     </row>
-    <row r="97" spans="1:31">
+    <row r="97" spans="1:32">
       <c r="A97" t="s">
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C97" s="2">
         <v>45403.36062178241</v>
@@ -10554,13 +10563,13 @@
         <v>1800</v>
       </c>
       <c r="H97" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I97" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J97" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K97">
         <v>121</v>
@@ -10599,7 +10608,7 @@
         <v>22.88333333</v>
       </c>
       <c r="W97" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X97">
         <v>-0.030278</v>
@@ -10626,12 +10635,12 @@
         <v>21.857097</v>
       </c>
     </row>
-    <row r="98" spans="1:31">
+    <row r="98" spans="1:32">
       <c r="A98" t="s">
         <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C98" s="2">
         <v>45403.36074664352</v>
@@ -10649,13 +10658,13 @@
         <v>1817</v>
       </c>
       <c r="H98" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J98" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K98">
         <v>96</v>
@@ -10682,7 +10691,7 @@
         <v>21.76666667</v>
       </c>
       <c r="W98" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X98">
         <v>-0.037222</v>
@@ -10709,12 +10718,12 @@
         <v>21.635857</v>
       </c>
     </row>
-    <row r="99" spans="1:31">
+    <row r="99" spans="1:32">
       <c r="A99" t="s">
         <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C99" s="2">
         <v>45403.36109293981</v>
@@ -10732,13 +10741,13 @@
         <v>1847</v>
       </c>
       <c r="H99" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J99" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K99">
         <v>82</v>
@@ -10765,7 +10774,7 @@
         <v>26.13333333</v>
       </c>
       <c r="W99" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X99">
         <v>0.145556</v>
@@ -10792,12 +10801,12 @@
         <v>21.090138</v>
       </c>
     </row>
-    <row r="100" spans="1:31">
+    <row r="100" spans="1:32">
       <c r="A100" t="s">
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C100" s="2">
         <v>45403.36144085648</v>
@@ -10815,13 +10824,13 @@
         <v>1877</v>
       </c>
       <c r="H100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J100" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K100">
         <v>100</v>
@@ -10848,7 +10857,7 @@
         <v>23.86666667</v>
       </c>
       <c r="W100" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X100">
         <v>-0.075556</v>
@@ -10874,13 +10883,16 @@
       <c r="AE100">
         <v>20.658157</v>
       </c>
-    </row>
-    <row r="101" spans="1:31">
+      <c r="AF100" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="101" spans="1:32">
       <c r="A101" t="s">
         <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C101" s="2">
         <v>45403.36178607639</v>
@@ -10898,13 +10910,13 @@
         <v>1907</v>
       </c>
       <c r="H101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J101" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K101">
         <v>99</v>
@@ -10931,7 +10943,7 @@
         <v>18.03333333</v>
       </c>
       <c r="W101" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X101">
         <v>-0.194444</v>
@@ -10958,12 +10970,12 @@
         <v>20.379968</v>
       </c>
     </row>
-    <row r="102" spans="1:31">
+    <row r="102" spans="1:32">
       <c r="A102" t="s">
         <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C102" s="2">
         <v>45403.36213509259</v>
@@ -10981,13 +10993,13 @@
         <v>1937</v>
       </c>
       <c r="H102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J102" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K102">
         <v>104</v>
@@ -11014,7 +11026,7 @@
         <v>20.56666667</v>
       </c>
       <c r="W102" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X102">
         <v>0.08444400000000001</v>
@@ -11041,12 +11053,12 @@
         <v>20.117877</v>
       </c>
     </row>
-    <row r="103" spans="1:31">
+    <row r="103" spans="1:32">
       <c r="A103" t="s">
         <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C103" s="2">
         <v>45403.36248055556</v>
@@ -11064,13 +11076,13 @@
         <v>1967</v>
       </c>
       <c r="H103" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J103" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K103">
         <v>144</v>
@@ -11097,7 +11109,7 @@
         <v>22.2</v>
       </c>
       <c r="W103" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X103">
         <v>0.054444</v>
@@ -11124,12 +11136,12 @@
         <v>19.904522</v>
       </c>
     </row>
-    <row r="104" spans="1:31">
+    <row r="104" spans="1:32">
       <c r="A104" t="s">
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C104" s="2">
         <v>45403.36282774305</v>
@@ -11147,13 +11159,13 @@
         <v>1997</v>
       </c>
       <c r="H104" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J104" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K104">
         <v>143</v>
@@ -11180,7 +11192,7 @@
         <v>15.86666667</v>
       </c>
       <c r="W104" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X104">
         <v>-0.211111</v>
@@ -11207,12 +11219,12 @@
         <v>19.797472</v>
       </c>
     </row>
-    <row r="105" spans="1:31">
+    <row r="105" spans="1:32">
       <c r="A105" t="s">
         <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C105" s="2">
         <v>45403.36317440972</v>
@@ -11230,13 +11242,13 @@
         <v>2027</v>
       </c>
       <c r="H105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I105" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J105" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K105">
         <v>147</v>
@@ -11263,7 +11275,7 @@
         <v>16.63333333</v>
       </c>
       <c r="W105" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X105">
         <v>0.025556</v>
@@ -11290,12 +11302,12 @@
         <v>19.726084</v>
       </c>
     </row>
-    <row r="106" spans="1:31">
+    <row r="106" spans="1:32">
       <c r="A106" t="s">
         <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C106" s="2">
         <v>45403.36352231482</v>
@@ -11313,13 +11325,13 @@
         <v>2057</v>
       </c>
       <c r="H106" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J106" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K106">
         <v>130</v>
@@ -11346,7 +11358,7 @@
         <v>16.83333333</v>
       </c>
       <c r="W106" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X106">
         <v>0.006667</v>
@@ -11373,12 +11385,12 @@
         <v>19.695812</v>
       </c>
     </row>
-    <row r="107" spans="1:31">
+    <row r="107" spans="1:32">
       <c r="A107" t="s">
         <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C107" s="2">
         <v>45403.36421915509</v>
@@ -11396,13 +11408,13 @@
         <v>2117</v>
       </c>
       <c r="H107" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J107" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K107">
         <v>129</v>
@@ -11429,7 +11441,7 @@
         <v>18.91666667</v>
       </c>
       <c r="W107" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X107">
         <v>0.034722</v>
@@ -11456,12 +11468,12 @@
         <v>19.774184</v>
       </c>
     </row>
-    <row r="108" spans="1:31">
+    <row r="108" spans="1:32">
       <c r="A108" t="s">
         <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C108" s="2">
         <v>45403.36440714121</v>
@@ -11479,13 +11491,13 @@
         <v>2130</v>
       </c>
       <c r="H108" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I108" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J108" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K108">
         <v>123</v>
@@ -11524,7 +11536,7 @@
         <v>19.90909091</v>
       </c>
       <c r="W108" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X108">
         <v>0.003007</v>
@@ -11551,12 +11563,12 @@
         <v>19.833561</v>
       </c>
     </row>
-    <row r="109" spans="1:31">
+    <row r="109" spans="1:32">
       <c r="A109" t="s">
         <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C109" s="2">
         <v>45403.36456484954</v>
@@ -11574,13 +11586,13 @@
         <v>2147</v>
       </c>
       <c r="H109" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I109" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J109" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K109">
         <v>110</v>
@@ -11607,7 +11619,7 @@
         <v>20.66666667</v>
       </c>
       <c r="W109" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X109">
         <v>0.025253</v>
@@ -11634,12 +11646,12 @@
         <v>19.895011</v>
       </c>
     </row>
-    <row r="110" spans="1:31">
+    <row r="110" spans="1:32">
       <c r="A110" t="s">
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C110" s="2">
         <v>45403.36491126157</v>
@@ -11657,13 +11669,13 @@
         <v>2177</v>
       </c>
       <c r="H110" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I110" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J110" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K110">
         <v>117</v>
@@ -11690,7 +11702,7 @@
         <v>21.13333333</v>
       </c>
       <c r="W110" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X110">
         <v>0.015556</v>
@@ -11717,12 +11729,12 @@
         <v>20.067667</v>
       </c>
     </row>
-    <row r="111" spans="1:31">
+    <row r="111" spans="1:32">
       <c r="A111" t="s">
         <v>25</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C111" s="2">
         <v>45403.36560518519</v>
@@ -11740,13 +11752,13 @@
         <v>2237</v>
       </c>
       <c r="H111" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I111" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J111" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K111">
         <v>142</v>
@@ -11773,7 +11785,7 @@
         <v>20.88333333</v>
       </c>
       <c r="W111" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X111">
         <v>-0.004167</v>
@@ -11800,12 +11812,12 @@
         <v>20.523624</v>
       </c>
     </row>
-    <row r="112" spans="1:31">
+    <row r="112" spans="1:32">
       <c r="A112" t="s">
         <v>25</v>
       </c>
       <c r="B112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C112" s="2">
         <v>45403.36579548611</v>
@@ -11823,13 +11835,13 @@
         <v>2250</v>
       </c>
       <c r="H112" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I112" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J112" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K112">
         <v>114</v>
@@ -11868,7 +11880,7 @@
         <v>21.13333333</v>
       </c>
       <c r="W112" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X112">
         <v>0.002083</v>
@@ -11900,7 +11912,7 @@
         <v>25</v>
       </c>
       <c r="B113" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C113" s="2">
         <v>45403.3663000926</v>
@@ -11918,13 +11930,13 @@
         <v>2297</v>
       </c>
       <c r="H113" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I113" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J113" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K113">
         <v>141</v>
@@ -11951,7 +11963,7 @@
         <v>20.51666667</v>
       </c>
       <c r="W113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X113">
         <v>-0.010278</v>
@@ -11983,7 +11995,7 @@
         <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C114" s="2">
         <v>45403.36648957176</v>
@@ -12001,13 +12013,13 @@
         <v>2310</v>
       </c>
       <c r="H114" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J114" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K114">
         <v>111</v>
@@ -12046,7 +12058,7 @@
         <v>19.58333333</v>
       </c>
       <c r="W114" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X114">
         <v>-0.015556</v>
@@ -12078,7 +12090,7 @@
         <v>25</v>
       </c>
       <c r="B115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C115" s="2">
         <v>45403.36718447917</v>
@@ -12096,13 +12108,13 @@
         <v>2370</v>
       </c>
       <c r="H115" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J115" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K115">
         <v>127</v>
@@ -12141,7 +12153,7 @@
         <v>23.81666667</v>
       </c>
       <c r="W115" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X115">
         <v>0.07055599999999999</v>
@@ -12173,7 +12185,7 @@
         <v>25</v>
       </c>
       <c r="B116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C116" s="2">
         <v>45403.36756590278</v>
@@ -12191,13 +12203,13 @@
         <v>2400</v>
       </c>
       <c r="H116" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J116" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K116">
         <v>119</v>
@@ -12236,7 +12248,7 @@
         <v>20.93333333</v>
       </c>
       <c r="W116" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X116">
         <v>-0.096111</v>
@@ -12268,7 +12280,7 @@
         <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C117" s="2">
         <v>45403.36787876157</v>
@@ -12286,13 +12298,13 @@
         <v>2430</v>
       </c>
       <c r="H117" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J117" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K117">
         <v>129</v>
@@ -12331,7 +12343,7 @@
         <v>19.76666667</v>
       </c>
       <c r="W117" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X117">
         <v>-0.038889</v>
@@ -12363,7 +12375,7 @@
         <v>25</v>
       </c>
       <c r="B118" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C118" s="2">
         <v>45403.368385</v>
@@ -12381,13 +12393,13 @@
         <v>2477</v>
       </c>
       <c r="H118" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I118" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J118" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K118">
         <v>111</v>
@@ -12414,7 +12426,7 @@
         <v>21.21666667</v>
       </c>
       <c r="W118" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X118">
         <v>0.008056000000000001</v>
@@ -12446,7 +12458,7 @@
         <v>25</v>
       </c>
       <c r="B119" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C119" s="2">
         <v>45403.36908070602</v>
@@ -12464,13 +12476,13 @@
         <v>2537</v>
       </c>
       <c r="H119" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I119" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J119" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K119">
         <v>80</v>
@@ -12497,7 +12509,7 @@
         <v>22.31666667</v>
       </c>
       <c r="W119" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X119">
         <v>0.018333</v>
@@ -12529,7 +12541,7 @@
         <v>25</v>
       </c>
       <c r="B120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C120" s="2">
         <v>45403.36942525463</v>
@@ -12547,13 +12559,13 @@
         <v>2567</v>
       </c>
       <c r="H120" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I120" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J120" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K120">
         <v>40</v>
@@ -12580,7 +12592,7 @@
         <v>29.3</v>
       </c>
       <c r="W120" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X120">
         <v>0.232778</v>
@@ -12612,7 +12624,7 @@
         <v>25</v>
       </c>
       <c r="B121" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C121" s="2">
         <v>45403.37046804398</v>
@@ -12630,13 +12642,13 @@
         <v>2657</v>
       </c>
       <c r="H121" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I121" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J121" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K121">
         <v>119</v>
@@ -12663,7 +12675,7 @@
         <v>26.8</v>
       </c>
       <c r="W121" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X121">
         <v>-0.027778</v>
@@ -12695,7 +12707,7 @@
         <v>25</v>
       </c>
       <c r="B122" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C122" s="2">
         <v>45403.37116125</v>
@@ -12713,13 +12725,13 @@
         <v>2717</v>
       </c>
       <c r="H122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I122" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J122" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K122">
         <v>128</v>
@@ -12746,7 +12758,7 @@
         <v>19.95</v>
       </c>
       <c r="W122" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X122">
         <v>-0.114167</v>
@@ -12778,7 +12790,7 @@
         <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C123" s="2">
         <v>45403.37151903935</v>
@@ -12796,13 +12808,13 @@
         <v>2747</v>
       </c>
       <c r="H123" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J123" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K123">
         <v>158</v>
@@ -12829,7 +12841,7 @@
         <v>19.26666667</v>
       </c>
       <c r="W123" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X123">
         <v>-0.022778</v>
@@ -12861,7 +12873,7 @@
         <v>25</v>
       </c>
       <c r="B124" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C124" s="2">
         <v>45403.3732447338</v>
@@ -12879,13 +12891,13 @@
         <v>2897</v>
       </c>
       <c r="H124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J124" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K124">
         <v>81</v>
@@ -12912,7 +12924,7 @@
         <v>19.55333333</v>
       </c>
       <c r="W124" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X124">
         <v>0.001911</v>
@@ -12944,7 +12956,7 @@
         <v>25</v>
       </c>
       <c r="B125" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C125" s="2">
         <v>45403.37463532407</v>
@@ -12962,13 +12974,13 @@
         <v>3017</v>
       </c>
       <c r="H125" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I125" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J125" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K125">
         <v>91</v>
@@ -12995,7 +13007,7 @@
         <v>19.60833333</v>
       </c>
       <c r="W125" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X125">
         <v>0.000458</v>
@@ -13027,7 +13039,7 @@
         <v>25</v>
       </c>
       <c r="B126" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C126" s="2">
         <v>45403.3760225463</v>
@@ -13045,13 +13057,13 @@
         <v>3137</v>
       </c>
       <c r="H126" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I126" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J126" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K126">
         <v>162</v>
@@ -13078,7 +13090,7 @@
         <v>20.91666667</v>
       </c>
       <c r="W126" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X126">
         <v>0.010903</v>
@@ -13110,7 +13122,7 @@
         <v>25</v>
       </c>
       <c r="B127" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C127" s="2">
         <v>45403.37741244213</v>
@@ -13128,13 +13140,13 @@
         <v>3257</v>
       </c>
       <c r="H127" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I127" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J127" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K127">
         <v>101</v>
@@ -13161,7 +13173,7 @@
         <v>19.225</v>
       </c>
       <c r="W127" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X127">
         <v>-0.014097</v>
@@ -13193,7 +13205,7 @@
         <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C128" s="2">
         <v>45403.37879991898</v>
@@ -13211,13 +13223,13 @@
         <v>3377</v>
       </c>
       <c r="H128" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I128" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J128" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K128">
         <v>346</v>
@@ -13244,7 +13256,7 @@
         <v>21.98333333</v>
       </c>
       <c r="W128" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X128">
         <v>0.022986</v>
@@ -13276,7 +13288,7 @@
         <v>25</v>
       </c>
       <c r="B129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C129" s="2">
         <v>45403.37914791667</v>
@@ -13294,13 +13306,13 @@
         <v>3407</v>
       </c>
       <c r="H129" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I129" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J129" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K129">
         <v>314</v>
@@ -13327,7 +13339,7 @@
         <v>19.13333333</v>
       </c>
       <c r="W129" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X129">
         <v>-0.095</v>
@@ -13359,7 +13371,7 @@
         <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C130" s="2">
         <v>45403.38018886574</v>
@@ -13377,13 +13389,13 @@
         <v>3497</v>
       </c>
       <c r="H130" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I130" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J130" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K130">
         <v>96</v>
@@ -13410,7 +13422,7 @@
         <v>19</v>
       </c>
       <c r="W130" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X130">
         <v>-0.001481</v>
@@ -13442,7 +13454,7 @@
         <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C131" s="2">
         <v>45403.38053690972</v>
@@ -13460,13 +13472,13 @@
         <v>3527</v>
       </c>
       <c r="H131" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I131" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J131" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K131">
         <v>121</v>
@@ -13493,7 +13505,7 @@
         <v>19.46666667</v>
       </c>
       <c r="W131" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X131">
         <v>0.015556</v>
@@ -13525,7 +13537,7 @@
         <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C132" s="2">
         <v>45403.38088469907</v>
@@ -13543,13 +13555,13 @@
         <v>3557</v>
       </c>
       <c r="H132" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I132" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J132" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K132">
         <v>352</v>
@@ -13576,7 +13588,7 @@
         <v>21</v>
       </c>
       <c r="W132" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X132">
         <v>0.051111</v>
@@ -13608,7 +13620,7 @@
         <v>25</v>
       </c>
       <c r="B133" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C133" s="2">
         <v>45403.3815791088</v>
@@ -13626,13 +13638,13 @@
         <v>3617</v>
       </c>
       <c r="H133" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I133" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J133" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K133">
         <v>92</v>
@@ -13659,7 +13671,7 @@
         <v>18.31666667</v>
       </c>
       <c r="W133" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X133">
         <v>-0.044722</v>
@@ -13691,7 +13703,7 @@
         <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C134" s="2">
         <v>45403.38192587963</v>
@@ -13709,13 +13721,13 @@
         <v>3647</v>
       </c>
       <c r="H134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I134" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J134" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K134">
         <v>94</v>
@@ -13742,7 +13754,7 @@
         <v>19.46666667</v>
       </c>
       <c r="W134" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X134">
         <v>0.038333</v>
@@ -13774,7 +13786,7 @@
         <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C135" s="2">
         <v>45403.38227145834</v>
@@ -13792,13 +13804,13 @@
         <v>3677</v>
       </c>
       <c r="H135" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I135" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J135" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K135">
         <v>116</v>
@@ -13825,7 +13837,7 @@
         <v>19.13333333</v>
       </c>
       <c r="W135" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X135">
         <v>-0.011111</v>
@@ -13857,7 +13869,7 @@
         <v>25</v>
       </c>
       <c r="B136" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C136" s="2">
         <v>45403.38296587963</v>
@@ -13875,13 +13887,13 @@
         <v>3737</v>
       </c>
       <c r="H136" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I136" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J136" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K136">
         <v>129</v>
@@ -13908,7 +13920,7 @@
         <v>19.36666667</v>
       </c>
       <c r="W136" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X136">
         <v>0.003889</v>
@@ -13940,7 +13952,7 @@
         <v>25</v>
       </c>
       <c r="B137" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C137" s="2">
         <v>45403.38331354166</v>
@@ -13958,13 +13970,13 @@
         <v>3767</v>
       </c>
       <c r="H137" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I137" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J137" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K137">
         <v>193</v>
@@ -13991,7 +14003,7 @@
         <v>19.8</v>
       </c>
       <c r="W137" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X137">
         <v>0.014444</v>
@@ -14023,7 +14035,7 @@
         <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C138" s="2">
         <v>45403.38366085648</v>
@@ -14041,13 +14053,13 @@
         <v>3797</v>
       </c>
       <c r="H138" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J138" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K138">
         <v>103</v>
@@ -14074,7 +14086,7 @@
         <v>19.66666667</v>
       </c>
       <c r="W138" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X138">
         <v>-0.004444</v>
@@ -14106,7 +14118,7 @@
         <v>25</v>
       </c>
       <c r="B139" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C139" s="2">
         <v>45403.384008125</v>
@@ -14124,13 +14136,13 @@
         <v>3827</v>
       </c>
       <c r="H139" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I139" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J139" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K139">
         <v>104</v>
@@ -14157,7 +14169,7 @@
         <v>18.83333333</v>
       </c>
       <c r="W139" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X139">
         <v>-0.027778</v>
@@ -14189,7 +14201,7 @@
         <v>25</v>
       </c>
       <c r="B140" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C140" s="2">
         <v>45403.38435752315</v>
@@ -14207,13 +14219,13 @@
         <v>3857</v>
       </c>
       <c r="H140" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I140" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J140" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K140">
         <v>152</v>
@@ -14240,7 +14252,7 @@
         <v>2.73333333</v>
       </c>
       <c r="W140" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X140">
         <v>-0.536667</v>
@@ -14274,10 +14286,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE86"/>
+  <dimension ref="A1:AF86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -14371,13 +14383,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2">
         <v>45403.38470376157</v>
@@ -14395,13 +14410,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K2">
         <v>139</v>
@@ -14428,7 +14443,7 @@
         <v>-93.3</v>
       </c>
       <c r="W2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Y2">
         <v>-93.3</v>
@@ -14437,12 +14452,12 @@
         <v>-93.359709</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>45403.38505405092</v>
@@ -14460,13 +14475,13 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K3">
         <v>46</v>
@@ -14493,7 +14508,7 @@
         <v>-92.53333333</v>
       </c>
       <c r="W3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X3">
         <v>0.025556</v>
@@ -14514,12 +14529,12 @@
         <v>-92.23400599999999</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2">
         <v>45403.38540138889</v>
@@ -14537,13 +14552,13 @@
         <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K4">
         <v>14</v>
@@ -14570,7 +14585,7 @@
         <v>-89.03333333</v>
       </c>
       <c r="W4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X4">
         <v>0.116667</v>
@@ -14597,12 +14612,12 @@
         <v>-89.19941</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>45403.38574840278</v>
@@ -14620,13 +14635,13 @@
         <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K5">
         <v>136</v>
@@ -14653,7 +14668,7 @@
         <v>-82.7</v>
       </c>
       <c r="W5" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X5">
         <v>0.211111</v>
@@ -14680,12 +14695,12 @@
         <v>-84.003912</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2">
         <v>45403.38609175926</v>
@@ -14703,13 +14718,13 @@
         <v>120</v>
       </c>
       <c r="H6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K6">
         <v>113</v>
@@ -14736,7 +14751,7 @@
         <v>-82</v>
       </c>
       <c r="W6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X6">
         <v>0.023333</v>
@@ -14763,12 +14778,12 @@
         <v>-79.846749</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>45403.38678726852</v>
@@ -14786,13 +14801,13 @@
         <v>180</v>
       </c>
       <c r="H7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K7">
         <v>273</v>
@@ -14819,7 +14834,7 @@
         <v>-73.40000000000001</v>
       </c>
       <c r="W7" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X7">
         <v>0.143333</v>
@@ -14846,12 +14861,12 @@
         <v>-74.151225</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2">
         <v>45403.38713508102</v>
@@ -14869,13 +14884,13 @@
         <v>210</v>
       </c>
       <c r="H8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K8">
         <v>110</v>
@@ -14902,7 +14917,7 @@
         <v>-69</v>
       </c>
       <c r="W8" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X8">
         <v>0.146667</v>
@@ -14929,12 +14944,12 @@
         <v>-70.062395</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2">
         <v>45403.38748087963</v>
@@ -14952,13 +14967,13 @@
         <v>240</v>
       </c>
       <c r="H9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J9" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K9">
         <v>145</v>
@@ -14985,7 +15000,7 @@
         <v>-65.3</v>
       </c>
       <c r="W9" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X9">
         <v>0.123333</v>
@@ -15012,12 +15027,12 @@
         <v>-64.75684699999999</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2">
         <v>45403.38817590278</v>
@@ -15035,13 +15050,13 @@
         <v>300</v>
       </c>
       <c r="H10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K10">
         <v>36</v>
@@ -15068,7 +15083,7 @@
         <v>-54.85</v>
       </c>
       <c r="W10" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X10">
         <v>0.174167</v>
@@ -15095,12 +15110,12 @@
         <v>-53.820552</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2">
         <v>45403.38852355324</v>
@@ -15118,13 +15133,13 @@
         <v>330</v>
       </c>
       <c r="H11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J11" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K11">
         <v>47</v>
@@ -15151,7 +15166,7 @@
         <v>-46.06666667</v>
       </c>
       <c r="W11" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X11">
         <v>0.292778</v>
@@ -15178,12 +15193,12 @@
         <v>-49.19554</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2">
         <v>45403.3888712037</v>
@@ -15201,13 +15216,13 @@
         <v>360</v>
       </c>
       <c r="H12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K12">
         <v>139</v>
@@ -15234,7 +15249,7 @@
         <v>-44.83333333</v>
       </c>
       <c r="W12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X12">
         <v>0.041111</v>
@@ -15261,12 +15276,12 @@
         <v>-45.06804</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2">
         <v>45403.38921841436</v>
@@ -15284,13 +15299,13 @@
         <v>390</v>
       </c>
       <c r="H13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J13" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K13">
         <v>147</v>
@@ -15317,7 +15332,7 @@
         <v>-44.4</v>
       </c>
       <c r="W13" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X13">
         <v>0.014444</v>
@@ -15344,12 +15359,12 @@
         <v>-41.54113</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2">
         <v>45403.3895640625</v>
@@ -15367,13 +15382,13 @@
         <v>420</v>
       </c>
       <c r="H14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I14" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J14" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K14">
         <v>129</v>
@@ -15400,7 +15415,7 @@
         <v>-42.9</v>
       </c>
       <c r="W14" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X14">
         <v>0.05</v>
@@ -15427,12 +15442,12 @@
         <v>-38.776839</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2">
         <v>45403.38991324074</v>
@@ -15450,13 +15465,13 @@
         <v>450</v>
       </c>
       <c r="H15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K15">
         <v>126</v>
@@ -15483,7 +15498,7 @@
         <v>-44.06666667</v>
       </c>
       <c r="W15" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X15">
         <v>-0.038889</v>
@@ -15510,12 +15525,12 @@
         <v>-36.634167</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2">
         <v>45403.39025761574</v>
@@ -15533,13 +15548,13 @@
         <v>480</v>
       </c>
       <c r="H16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I16" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J16" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K16">
         <v>122</v>
@@ -15566,7 +15581,7 @@
         <v>-42.1</v>
       </c>
       <c r="W16" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X16">
         <v>0.065556</v>
@@ -15598,7 +15613,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2">
         <v>45403.39048606482</v>
@@ -15616,13 +15631,13 @@
         <v>493</v>
       </c>
       <c r="H17" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I17" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J17" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K17">
         <v>139</v>
@@ -15661,7 +15676,7 @@
         <v>-2.33589744</v>
       </c>
       <c r="W17" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X17">
         <v>0.020392</v>
@@ -15693,7 +15708,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>45403.39060597222</v>
@@ -15711,13 +15726,13 @@
         <v>510</v>
       </c>
       <c r="H18" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I18" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J18" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K18">
         <v>103</v>
@@ -15744,7 +15759,7 @@
         <v>-38.93333333</v>
       </c>
       <c r="W18" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X18">
         <v>-1.219915</v>
@@ -15776,7 +15791,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2">
         <v>45403.39095601852</v>
@@ -15794,13 +15809,13 @@
         <v>540</v>
       </c>
       <c r="H19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I19" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J19" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K19">
         <v>135</v>
@@ -15827,7 +15842,7 @@
         <v>-38.5</v>
       </c>
       <c r="W19" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X19">
         <v>0.014444</v>
@@ -15859,7 +15874,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>45403.39130103009</v>
@@ -15877,13 +15892,13 @@
         <v>570</v>
       </c>
       <c r="H20" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I20" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J20" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K20">
         <v>84</v>
@@ -15910,7 +15925,7 @@
         <v>-36.76666667</v>
       </c>
       <c r="W20" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X20">
         <v>0.057778</v>
@@ -15942,7 +15957,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2">
         <v>45403.39199434028</v>
@@ -15960,13 +15975,13 @@
         <v>630</v>
       </c>
       <c r="H21" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I21" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J21" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K21">
         <v>115</v>
@@ -15993,7 +16008,7 @@
         <v>-35.76666667</v>
       </c>
       <c r="W21" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X21">
         <v>0.016667</v>
@@ -16025,7 +16040,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>45403.39234143519</v>
@@ -16043,13 +16058,13 @@
         <v>660</v>
       </c>
       <c r="H22" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I22" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J22" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K22">
         <v>109</v>
@@ -16076,7 +16091,7 @@
         <v>-34.43333333</v>
       </c>
       <c r="W22" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X22">
         <v>0.044444</v>
@@ -16108,7 +16123,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2">
         <v>45403.39303620371</v>
@@ -16126,13 +16141,13 @@
         <v>720</v>
       </c>
       <c r="H23" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I23" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J23" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="K23">
         <v>109</v>
@@ -16159,7 +16174,7 @@
         <v>-31.71666667</v>
       </c>
       <c r="W23" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X23">
         <v>0.045278</v>
@@ -16191,7 +16206,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2">
         <v>45403.39338446759</v>
@@ -16209,13 +16224,13 @@
         <v>750</v>
       </c>
       <c r="H24" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I24" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J24" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K24">
         <v>96</v>
@@ -16242,7 +16257,7 @@
         <v>-30.96666667</v>
       </c>
       <c r="W24" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X24">
         <v>0.025</v>
@@ -16274,7 +16289,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2">
         <v>45403.39357175926</v>
@@ -16292,13 +16307,13 @@
         <v>763</v>
       </c>
       <c r="H25" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I25" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J25" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K25">
         <v>107</v>
@@ -16337,7 +16352,7 @@
         <v>-34.5962963</v>
       </c>
       <c r="W25" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X25">
         <v>-0.013443</v>
@@ -16369,7 +16384,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2">
         <v>45403.39407809028</v>
@@ -16387,13 +16402,13 @@
         <v>810</v>
       </c>
       <c r="H26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I26" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J26" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K26">
         <v>133</v>
@@ -16420,7 +16435,7 @@
         <v>-30.46666667</v>
       </c>
       <c r="W26" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X26">
         <v>0.068827</v>
@@ -16452,7 +16467,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="2">
         <v>45403.39442841435</v>
@@ -16470,13 +16485,13 @@
         <v>840</v>
       </c>
       <c r="H27" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I27" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J27" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K27">
         <v>127</v>
@@ -16503,7 +16518,7 @@
         <v>-29.83333333</v>
       </c>
       <c r="W27" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X27">
         <v>0.021111</v>
@@ -16535,7 +16550,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>45403.39511917824</v>
@@ -16553,13 +16568,13 @@
         <v>900</v>
       </c>
       <c r="H28" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I28" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J28" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K28">
         <v>105</v>
@@ -16586,7 +16601,7 @@
         <v>-28.93333333</v>
       </c>
       <c r="W28" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X28">
         <v>0.015</v>
@@ -16618,7 +16633,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2">
         <v>45403.39546671297</v>
@@ -16636,13 +16651,13 @@
         <v>930</v>
       </c>
       <c r="H29" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I29" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J29" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K29">
         <v>118</v>
@@ -16669,7 +16684,7 @@
         <v>-27.9</v>
       </c>
       <c r="W29" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X29">
         <v>0.034444</v>
@@ -16701,7 +16716,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>45403.39616402778</v>
@@ -16719,13 +16734,13 @@
         <v>990</v>
       </c>
       <c r="H30" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I30" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J30" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K30">
         <v>122</v>
@@ -16752,7 +16767,7 @@
         <v>-25.65</v>
       </c>
       <c r="W30" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X30">
         <v>0.0375</v>
@@ -16784,7 +16799,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>45403.3965112037</v>
@@ -16802,13 +16817,13 @@
         <v>1020</v>
       </c>
       <c r="H31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K31">
         <v>111</v>
@@ -16835,7 +16850,7 @@
         <v>-24.93333333</v>
       </c>
       <c r="W31" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X31">
         <v>0.023889</v>
@@ -16867,7 +16882,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>45403.39720318287</v>
@@ -16885,13 +16900,13 @@
         <v>1080</v>
       </c>
       <c r="H32" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I32" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J32" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K32">
         <v>111</v>
@@ -16918,7 +16933,7 @@
         <v>-24.33333333</v>
       </c>
       <c r="W32" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X32">
         <v>0.01</v>
@@ -16950,7 +16965,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2">
         <v>45403.39755100694</v>
@@ -16968,13 +16983,13 @@
         <v>1110</v>
       </c>
       <c r="H33" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I33" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J33" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K33">
         <v>126</v>
@@ -17001,7 +17016,7 @@
         <v>-23.63333333</v>
       </c>
       <c r="W33" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X33">
         <v>0.023333</v>
@@ -17033,7 +17048,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>45403.39789850695</v>
@@ -17051,13 +17066,13 @@
         <v>1140</v>
       </c>
       <c r="H34" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I34" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J34" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K34">
         <v>141</v>
@@ -17084,7 +17099,7 @@
         <v>-22.96666667</v>
       </c>
       <c r="W34" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X34">
         <v>0.022222</v>
@@ -17116,7 +17131,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>45403.39824560185</v>
@@ -17134,13 +17149,13 @@
         <v>1170</v>
       </c>
       <c r="H35" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I35" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K35">
         <v>140</v>
@@ -17167,7 +17182,7 @@
         <v>-23.3</v>
       </c>
       <c r="W35" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X35">
         <v>-0.011111</v>
@@ -17199,7 +17214,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2">
         <v>45403.39859101852</v>
@@ -17217,13 +17232,13 @@
         <v>1200</v>
       </c>
       <c r="H36" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I36" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J36" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K36">
         <v>127</v>
@@ -17250,7 +17265,7 @@
         <v>-23.73333333</v>
       </c>
       <c r="W36" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X36">
         <v>-0.014444</v>
@@ -17282,7 +17297,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2">
         <v>45403.3989393287</v>
@@ -17300,13 +17315,13 @@
         <v>1230</v>
       </c>
       <c r="H37" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I37" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J37" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K37">
         <v>137</v>
@@ -17333,7 +17348,7 @@
         <v>-23.3</v>
       </c>
       <c r="W37" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X37">
         <v>0.014444</v>
@@ -17365,7 +17380,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>45403.39928760417</v>
@@ -17383,13 +17398,13 @@
         <v>1260</v>
       </c>
       <c r="H38" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I38" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J38" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K38">
         <v>141</v>
@@ -17416,7 +17431,7 @@
         <v>-23.4</v>
       </c>
       <c r="W38" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X38">
         <v>-0.003333</v>
@@ -17448,7 +17463,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2">
         <v>45403.39963373842</v>
@@ -17466,13 +17481,13 @@
         <v>1290</v>
       </c>
       <c r="H39" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I39" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J39" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K39">
         <v>143</v>
@@ -17499,7 +17514,7 @@
         <v>-22.96666667</v>
       </c>
       <c r="W39" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X39">
         <v>0.014444</v>
@@ -17531,7 +17546,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>45403.39998326389</v>
@@ -17549,13 +17564,13 @@
         <v>1320</v>
       </c>
       <c r="H40" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I40" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J40" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K40">
         <v>143</v>
@@ -17582,7 +17597,7 @@
         <v>-22.1</v>
       </c>
       <c r="W40" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X40">
         <v>0.028889</v>
@@ -17614,7 +17629,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2">
         <v>45403.40032832176</v>
@@ -17632,13 +17647,13 @@
         <v>1350</v>
       </c>
       <c r="H41" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I41" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J41" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K41">
         <v>142</v>
@@ -17665,7 +17680,7 @@
         <v>-21.43333333</v>
       </c>
       <c r="W41" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X41">
         <v>0.022222</v>
@@ -17697,7 +17712,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>45403.40067550926</v>
@@ -17715,13 +17730,13 @@
         <v>1380</v>
       </c>
       <c r="H42" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I42" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J42" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K42">
         <v>140</v>
@@ -17748,7 +17763,7 @@
         <v>-21.33333333</v>
       </c>
       <c r="W42" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X42">
         <v>0.003333</v>
@@ -17780,7 +17795,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43" s="2">
         <v>45403.40102575231</v>
@@ -17798,13 +17813,13 @@
         <v>1410</v>
       </c>
       <c r="H43" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I43" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J43" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K43">
         <v>131</v>
@@ -17831,7 +17846,7 @@
         <v>-20.33333333</v>
       </c>
       <c r="W43" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X43">
         <v>0.033333</v>
@@ -17863,7 +17878,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2">
         <v>45403.40136972223</v>
@@ -17881,13 +17896,13 @@
         <v>1440</v>
       </c>
       <c r="H44" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I44" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J44" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K44">
         <v>130</v>
@@ -17914,7 +17929,7 @@
         <v>-20.23333333</v>
       </c>
       <c r="W44" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X44">
         <v>0.003333</v>
@@ -17946,7 +17961,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" s="2">
         <v>45403.40171717593</v>
@@ -17964,13 +17979,13 @@
         <v>1470</v>
       </c>
       <c r="H45" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I45" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J45" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K45">
         <v>144</v>
@@ -17997,7 +18012,7 @@
         <v>-19.26666667</v>
       </c>
       <c r="W45" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X45">
         <v>0.032222</v>
@@ -18029,7 +18044,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2">
         <v>45403.40206369213</v>
@@ -18047,13 +18062,13 @@
         <v>1500</v>
       </c>
       <c r="H46" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I46" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J46" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K46">
         <v>150</v>
@@ -18080,7 +18095,7 @@
         <v>-19.66666667</v>
       </c>
       <c r="W46" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X46">
         <v>-0.013333</v>
@@ -18112,7 +18127,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C47" s="2">
         <v>45403.40241096065</v>
@@ -18130,13 +18145,13 @@
         <v>1530</v>
       </c>
       <c r="H47" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I47" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J47" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K47">
         <v>141</v>
@@ -18163,7 +18178,7 @@
         <v>-19.46666667</v>
       </c>
       <c r="W47" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X47">
         <v>0.006667</v>
@@ -18195,7 +18210,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="2">
         <v>45403.40275898148</v>
@@ -18213,13 +18228,13 @@
         <v>1560</v>
       </c>
       <c r="H48" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I48" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J48" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K48">
         <v>138</v>
@@ -18246,7 +18261,7 @@
         <v>-20.36666667</v>
       </c>
       <c r="W48" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X48">
         <v>-0.03</v>
@@ -18278,7 +18293,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>45403.40310667824</v>
@@ -18296,13 +18311,13 @@
         <v>1590</v>
       </c>
       <c r="H49" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I49" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J49" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K49">
         <v>139</v>
@@ -18329,7 +18344,7 @@
         <v>-19.66666667</v>
       </c>
       <c r="W49" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X49">
         <v>0.023333</v>
@@ -18361,7 +18376,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" s="2">
         <v>45403.40345479167</v>
@@ -18379,13 +18394,13 @@
         <v>1620</v>
       </c>
       <c r="H50" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I50" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J50" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K50">
         <v>135</v>
@@ -18412,7 +18427,7 @@
         <v>-20.36666667</v>
       </c>
       <c r="W50" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X50">
         <v>-0.023333</v>
@@ -18444,7 +18459,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>45403.40380133102</v>
@@ -18462,13 +18477,13 @@
         <v>1650</v>
       </c>
       <c r="H51" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I51" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J51" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K51">
         <v>150</v>
@@ -18495,7 +18510,7 @@
         <v>-20.23333333</v>
       </c>
       <c r="W51" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X51">
         <v>0.004444</v>
@@ -18527,7 +18542,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" s="2">
         <v>45403.40414807871</v>
@@ -18545,13 +18560,13 @@
         <v>1680</v>
       </c>
       <c r="H52" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I52" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J52" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="K52">
         <v>143</v>
@@ -18578,7 +18593,7 @@
         <v>-19.8</v>
       </c>
       <c r="W52" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X52">
         <v>0.014444</v>
@@ -18610,7 +18625,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>45403.40449873843</v>
@@ -18628,13 +18643,13 @@
         <v>1710</v>
       </c>
       <c r="H53" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I53" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J53" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K53">
         <v>147</v>
@@ -18661,7 +18676,7 @@
         <v>-20</v>
       </c>
       <c r="W53" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X53">
         <v>-0.006667</v>
@@ -18693,7 +18708,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C54" s="2">
         <v>45403.40484334491</v>
@@ -18711,13 +18726,13 @@
         <v>1740</v>
       </c>
       <c r="H54" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I54" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J54" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K54">
         <v>141</v>
@@ -18744,7 +18759,7 @@
         <v>-19.7</v>
       </c>
       <c r="W54" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X54">
         <v>0.01</v>
@@ -18776,7 +18791,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>45403.40518871527</v>
@@ -18794,13 +18809,13 @@
         <v>1770</v>
       </c>
       <c r="H55" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I55" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J55" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="K55">
         <v>143</v>
@@ -18827,7 +18842,7 @@
         <v>-19.03333333</v>
       </c>
       <c r="W55" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X55">
         <v>0.022222</v>
@@ -18859,7 +18874,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C56" s="2">
         <v>45403.40553603009</v>
@@ -18877,13 +18892,13 @@
         <v>1800</v>
       </c>
       <c r="H56" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I56" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J56" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K56">
         <v>157</v>
@@ -18910,7 +18925,7 @@
         <v>-18.8</v>
       </c>
       <c r="W56" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X56">
         <v>0.007778</v>
@@ -18942,7 +18957,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>45403.40588310185</v>
@@ -18960,13 +18975,13 @@
         <v>1830</v>
       </c>
       <c r="H57" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I57" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J57" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K57">
         <v>146</v>
@@ -18993,7 +19008,7 @@
         <v>-18.16666667</v>
       </c>
       <c r="W57" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X57">
         <v>0.021111</v>
@@ -19025,7 +19040,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="2">
         <v>45403.4065787037</v>
@@ -19043,13 +19058,13 @@
         <v>1890</v>
       </c>
       <c r="H58" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I58" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J58" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K58">
         <v>165</v>
@@ -19076,7 +19091,7 @@
         <v>-17.38333333</v>
       </c>
       <c r="W58" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X58">
         <v>0.013056</v>
@@ -19108,7 +19123,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2">
         <v>45403.40692917824</v>
@@ -19126,13 +19141,13 @@
         <v>1920</v>
       </c>
       <c r="H59" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I59" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J59" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K59">
         <v>151</v>
@@ -19159,7 +19174,7 @@
         <v>-16.83333333</v>
       </c>
       <c r="W59" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X59">
         <v>0.018333</v>
@@ -19191,7 +19206,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>45403.40727283565</v>
@@ -19209,13 +19224,13 @@
         <v>1950</v>
       </c>
       <c r="H60" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I60" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J60" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K60">
         <v>137</v>
@@ -19242,7 +19257,7 @@
         <v>-17.2</v>
       </c>
       <c r="W60" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X60">
         <v>-0.012222</v>
@@ -19274,7 +19289,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="2">
         <v>45403.40761988426</v>
@@ -19292,13 +19307,13 @@
         <v>1980</v>
       </c>
       <c r="H61" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I61" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J61" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K61">
         <v>163</v>
@@ -19325,7 +19340,7 @@
         <v>-16.73333333</v>
       </c>
       <c r="W61" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X61">
         <v>0.015556</v>
@@ -19357,7 +19372,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2">
         <v>45403.40796920139</v>
@@ -19375,13 +19390,13 @@
         <v>2010</v>
       </c>
       <c r="H62" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I62" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J62" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K62">
         <v>158</v>
@@ -19408,7 +19423,7 @@
         <v>-17.03333333</v>
       </c>
       <c r="W62" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X62">
         <v>-0.01</v>
@@ -19440,7 +19455,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C63" s="2">
         <v>45403.40831346065</v>
@@ -19458,13 +19473,13 @@
         <v>2040</v>
       </c>
       <c r="H63" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I63" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J63" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K63">
         <v>150</v>
@@ -19491,7 +19506,7 @@
         <v>-17.06666667</v>
       </c>
       <c r="W63" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X63">
         <v>-0.001111</v>
@@ -19523,7 +19538,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2">
         <v>45403.4086615162</v>
@@ -19541,13 +19556,13 @@
         <v>2070</v>
       </c>
       <c r="H64" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I64" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J64" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K64">
         <v>162</v>
@@ -19574,7 +19589,7 @@
         <v>-17.16666667</v>
       </c>
       <c r="W64" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X64">
         <v>-0.003333</v>
@@ -19606,7 +19621,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2">
         <v>45403.4090116088</v>
@@ -19624,13 +19639,13 @@
         <v>2100</v>
       </c>
       <c r="H65" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I65" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J65" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K65">
         <v>174</v>
@@ -19657,7 +19672,7 @@
         <v>-17.2</v>
       </c>
       <c r="W65" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X65">
         <v>-0.001111</v>
@@ -19689,7 +19704,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2">
         <v>45403.40935710648</v>
@@ -19707,13 +19722,13 @@
         <v>2130</v>
       </c>
       <c r="H66" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I66" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J66" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K66">
         <v>156</v>
@@ -19740,7 +19755,7 @@
         <v>-16.93333333</v>
       </c>
       <c r="W66" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X66">
         <v>0.008888999999999999</v>
@@ -19772,7 +19787,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2">
         <v>45403.40970434028</v>
@@ -19790,13 +19805,13 @@
         <v>2160</v>
       </c>
       <c r="H67" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I67" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J67" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K67">
         <v>154</v>
@@ -19823,7 +19838,7 @@
         <v>-16.96666667</v>
       </c>
       <c r="W67" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X67">
         <v>-0.001111</v>
@@ -19855,7 +19870,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2">
         <v>45403.4100522338</v>
@@ -19873,13 +19888,13 @@
         <v>2190</v>
       </c>
       <c r="H68" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I68" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J68" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K68">
         <v>139</v>
@@ -19906,7 +19921,7 @@
         <v>-17.4</v>
       </c>
       <c r="W68" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X68">
         <v>-0.014444</v>
@@ -19938,7 +19953,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2">
         <v>45403.41040427083</v>
@@ -19956,13 +19971,13 @@
         <v>2220</v>
       </c>
       <c r="H69" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I69" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J69" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K69">
         <v>163</v>
@@ -19989,7 +20004,7 @@
         <v>-16.5</v>
       </c>
       <c r="W69" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X69">
         <v>0.03</v>
@@ -20021,7 +20036,7 @@
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2">
         <v>45403.4110910301</v>
@@ -20039,13 +20054,13 @@
         <v>2280</v>
       </c>
       <c r="H70" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I70" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J70" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K70">
         <v>166</v>
@@ -20072,7 +20087,7 @@
         <v>-16.63333333</v>
       </c>
       <c r="W70" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X70">
         <v>-0.002222</v>
@@ -20104,7 +20119,7 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2">
         <v>45403.41143875</v>
@@ -20122,13 +20137,13 @@
         <v>2310</v>
       </c>
       <c r="H71" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I71" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J71" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K71">
         <v>167</v>
@@ -20155,7 +20170,7 @@
         <v>-16.26666667</v>
       </c>
       <c r="W71" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X71">
         <v>0.012222</v>
@@ -20187,7 +20202,7 @@
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2">
         <v>45403.41178738426</v>
@@ -20205,13 +20220,13 @@
         <v>2340</v>
       </c>
       <c r="H72" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I72" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J72" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K72">
         <v>137</v>
@@ -20238,7 +20253,7 @@
         <v>-15.86666667</v>
       </c>
       <c r="W72" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X72">
         <v>0.013333</v>
@@ -20270,7 +20285,7 @@
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2">
         <v>45403.41213525463</v>
@@ -20288,13 +20303,13 @@
         <v>2370</v>
       </c>
       <c r="H73" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I73" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J73" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K73">
         <v>140</v>
@@ -20321,7 +20336,7 @@
         <v>-16.1</v>
       </c>
       <c r="W73" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X73">
         <v>-0.007778</v>
@@ -20353,7 +20368,7 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="2">
         <v>45403.41248388889</v>
@@ -20371,13 +20386,13 @@
         <v>2400</v>
       </c>
       <c r="H74" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I74" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J74" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K74">
         <v>157</v>
@@ -20404,7 +20419,7 @@
         <v>-15.3</v>
       </c>
       <c r="W74" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X74">
         <v>0.026667</v>
@@ -20436,7 +20451,7 @@
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="2">
         <v>45403.41282869213</v>
@@ -20454,13 +20469,13 @@
         <v>2430</v>
       </c>
       <c r="H75" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I75" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J75" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K75">
         <v>171</v>
@@ -20487,7 +20502,7 @@
         <v>-15.2</v>
       </c>
       <c r="W75" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X75">
         <v>0.003333</v>
@@ -20519,7 +20534,7 @@
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="2">
         <v>45403.41317821759</v>
@@ -20537,13 +20552,13 @@
         <v>2460</v>
       </c>
       <c r="H76" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I76" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J76" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K76">
         <v>136</v>
@@ -20570,7 +20585,7 @@
         <v>-15.1</v>
       </c>
       <c r="W76" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X76">
         <v>0.003333</v>
@@ -20602,7 +20617,7 @@
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2">
         <v>45403.41352417824</v>
@@ -20620,13 +20635,13 @@
         <v>2490</v>
       </c>
       <c r="H77" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I77" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J77" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K77">
         <v>123</v>
@@ -20653,7 +20668,7 @@
         <v>-15.63333333</v>
       </c>
       <c r="W77" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X77">
         <v>-0.017778</v>
@@ -20685,7 +20700,7 @@
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C78" s="2">
         <v>45403.41387609953</v>
@@ -20703,13 +20718,13 @@
         <v>2520</v>
       </c>
       <c r="H78" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I78" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J78" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K78">
         <v>160</v>
@@ -20736,7 +20751,7 @@
         <v>-14.43333333</v>
       </c>
       <c r="W78" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X78">
         <v>0.04</v>
@@ -20768,7 +20783,7 @@
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2">
         <v>45403.41421701389</v>
@@ -20786,13 +20801,13 @@
         <v>2550</v>
       </c>
       <c r="H79" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I79" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J79" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K79">
         <v>122</v>
@@ -20819,7 +20834,7 @@
         <v>-14.56666667</v>
       </c>
       <c r="W79" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X79">
         <v>-0.004444</v>
@@ -20851,7 +20866,7 @@
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="2">
         <v>45403.41456357639</v>
@@ -20869,13 +20884,13 @@
         <v>2580</v>
       </c>
       <c r="H80" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I80" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J80" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K80">
         <v>103</v>
@@ -20902,7 +20917,7 @@
         <v>-14.3</v>
       </c>
       <c r="W80" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X80">
         <v>0.008888999999999999</v>
@@ -20934,7 +20949,7 @@
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="2">
         <v>45403.41491677083</v>
@@ -20952,13 +20967,13 @@
         <v>2610</v>
       </c>
       <c r="H81" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I81" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J81" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K81">
         <v>90</v>
@@ -20985,7 +21000,7 @@
         <v>-15.43333333</v>
       </c>
       <c r="W81" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X81">
         <v>-0.037778</v>
@@ -21017,7 +21032,7 @@
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C82" s="2">
         <v>45403.41560888889</v>
@@ -21035,13 +21050,13 @@
         <v>2670</v>
       </c>
       <c r="H82" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I82" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J82" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K82">
         <v>68</v>
@@ -21068,7 +21083,7 @@
         <v>-15.15</v>
       </c>
       <c r="W82" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X82">
         <v>0.004722</v>
@@ -21100,7 +21115,7 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C83" s="2">
         <v>45403.41595309028</v>
@@ -21118,13 +21133,13 @@
         <v>2700</v>
       </c>
       <c r="H83" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I83" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J83" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K83">
         <v>148</v>
@@ -21151,7 +21166,7 @@
         <v>-14.86666667</v>
       </c>
       <c r="W83" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X83">
         <v>0.009443999999999999</v>
@@ -21183,7 +21198,7 @@
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C84" s="2">
         <v>45403.41630097223</v>
@@ -21201,13 +21216,13 @@
         <v>2730</v>
       </c>
       <c r="H84" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I84" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J84" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K84">
         <v>93</v>
@@ -21234,7 +21249,7 @@
         <v>-14.66666667</v>
       </c>
       <c r="W84" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X84">
         <v>0.006667</v>
@@ -21266,7 +21281,7 @@
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="2">
         <v>45403.41664903935</v>
@@ -21284,13 +21299,13 @@
         <v>2760</v>
       </c>
       <c r="H85" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I85" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J85" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K85">
         <v>349</v>
@@ -21317,7 +21332,7 @@
         <v>-15.1</v>
       </c>
       <c r="W85" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X85">
         <v>-0.014444</v>
@@ -21349,7 +21364,7 @@
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C86" s="2">
         <v>45403.41734554398</v>
@@ -21367,13 +21382,13 @@
         <v>2820</v>
       </c>
       <c r="H86" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I86" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J86" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K86">
         <v>13</v>
@@ -21400,7 +21415,7 @@
         <v>-14</v>
       </c>
       <c r="W86" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X86">
         <v>0.018333</v>

--- a/www/flightdata/xlsx/eoss-357.xlsx
+++ b/www/flightdata/xlsx/eoss-357.xlsx
@@ -2175,7 +2175,7 @@
         <v>27295.45</v>
       </c>
       <c r="I2">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
